--- a/docs/costs/robot_build_costs.xlsx
+++ b/docs/costs/robot_build_costs.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="523">
   <si>
     <t xml:space="preserve">Robot build costs</t>
   </si>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">• Prices with confidence 'estimate' on the Prices sheet are typical store prices where no listing could be read; check them before ordering. Amazon.ca was not readable by the price search and is often cheaper for multi-packs.</t>
   </si>
   <si>
-    <t xml:space="preserve">• PETG and print hours: arm from its latest slices; rover from its round-2 slices; hexapod estimated. They change with each design round.</t>
+    <t xml:space="preserve">• PETG and print hours: arm from its round-3 slices (the new claw is heavier); rover from its round-2 slices; hexapod estimated. They change with each design round.</t>
   </si>
   <si>
     <t xml:space="preserve">Prices (CAD, before tax and shipping)</t>
@@ -1002,6 +1002,18 @@
     <t xml:space="preserve">Need 2 (A) = $2.72. No 50 cm lead at RobotShop; this is 10 cm longer than spec. Pack size not stated (assumed single). Lynxmotion SEA-03 24 in is $2.79. · https://ca.robotshop.com/products/servo-extension-cable-600mm</t>
   </si>
   <si>
+    <t xml:space="preserve">stripboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stripboard + headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stripboard ≈ 50 × 70 mm + 40-pin male header strip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronics or hardware store (typical)</t>
+  </si>
+  <si>
     <t xml:space="preserve">switch10a</t>
   </si>
   <si>
@@ -1038,6 +1050,15 @@
     <t xml:space="preserve">Camera or hardware store (typical)</t>
   </si>
   <si>
+    <t xml:space="preserve">tiemount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable-tie mounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adhesive cable-tie mounts, pack of 10</t>
+  </si>
+  <si>
     <t xml:space="preserve">toggle</t>
   </si>
   <si>
@@ -1092,6 +1113,15 @@
     <t xml:space="preserve">Straight connectors: no right-angle USB-C to A 2 m found at a readable Canadian retailer. Page says it is thinner and more flexible than the USB 3.1 version. Cheaper alt: Canada Robotix USB 3.0 A-to-C 2 m $9.99 (in stock; likely stiffer). · https://ca.robotshop.com/products/reversible-usb-a-to-usb-c-cable-2m</t>
   </si>
   <si>
+    <t xml:space="preserve">usbra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-angle USB cable (ESP32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-angle micro-USB or USB-C cable, 1 m</t>
+  </si>
+  <si>
     <t xml:space="preserve">velcro</t>
   </si>
   <si>
@@ -1104,6 +1134,15 @@
     <t xml:space="preserve">Need 2 (R1 + H1): one pack. Canadian (.ca) FPV shop; the page displayed USD (US$6.42 x 1.4004 = CA$8.99, probably the native CAD price). In stock (348). No 20 mm straps at RobotShop/Canada Robotix/BC Robotics; Home Depot/RONA VELCRO ONE-WRAP 3/4 in listings showed no price. · https://rotorvillage.ca/rvs-kevlar-battery-strap-2pk/</t>
   </si>
   <si>
+    <t xml:space="preserve">wire18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 AWG silicone wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicone wire 18 AWG, red and black, 1 m each</t>
+  </si>
+  <si>
     <t xml:space="preserve">wire22</t>
   </si>
   <si>
@@ -1194,6 +1233,9 @@
     <t xml:space="preserve">MG996R metal-gear servo (base, shoulder, elbow)</t>
   </si>
   <si>
+    <t xml:space="preserve">Keep the bags: Ø25 disc horn (base), double-arm horns</t>
+  </si>
+  <si>
     <t xml:space="preserve">MG90S metal-gear micro servo (wrist, claw)</t>
   </si>
   <si>
@@ -1221,10 +1263,16 @@
     <t xml:space="preserve">Inline blade-fuse holder + 5 A blade</t>
   </si>
   <si>
-    <t xml:space="preserve">Power bus (lever connectors) + 18 AWG wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep review 01-S8: no servo power through Dupont jumpers</t>
+    <t xml:space="preserve">Power bus: stripboard ≈ 50 × 30 mm + 3-pin male headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or a 5-way terminal strip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicone wire 18-20 AWG, red and black, 1 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servo power never runs through Dupont jumpers</t>
   </si>
   <si>
     <t xml:space="preserve">1000 µF electrolytic capacitor</t>
@@ -1239,19 +1287,16 @@
     <t xml:space="preserve">Wiring</t>
   </si>
   <si>
-    <t xml:space="preserve">Servo extension 50-60 cm (claw, wrist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep review 03-SYS-10</t>
+    <t xml:space="preserve">Servo extension 50 cm (claw, wrist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priced at 60 cm</t>
   </si>
   <si>
     <t xml:space="preserve">Servo extension 30 cm (elbow)</t>
   </si>
   <si>
-    <t xml:space="preserve">Deep review 01-S7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumper wires F-F</t>
+    <t xml:space="preserve">Jumper wires F-F (signals only)</t>
   </si>
   <si>
     <t xml:space="preserve">10 kΩ pull-down resistors (optional)</t>
@@ -1260,10 +1305,19 @@
     <t xml:space="preserve">Share of a resistor kit</t>
   </si>
   <si>
-    <t xml:space="preserve">Flexible USB-C to USB-A cable, 2 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For the Brio</t>
+    <t xml:space="preserve">Right-angle micro-USB/USB-C cable for the ESP32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thin right-angle USB-C to USB-A cable, 2 m (Brio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priced for a straight 2 m cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip ties, adhesive tie mounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adhesive cable-tie mounts</t>
   </si>
   <si>
     <t xml:space="preserve">Heat-shrink tubing</t>
@@ -1275,244 +1329,253 @@
     <t xml:space="preserve">Fasteners</t>
   </si>
   <si>
-    <t xml:space="preserve">M3 × 16 socket head (horn clamps) and other M3 machine screws</t>
+    <t xml:space="preserve">M3 × 14 socket head (horn clamps) and other M3 machine screws</t>
   </si>
   <si>
     <t xml:space="preserve">Share of a 240-piece kit</t>
   </si>
   <si>
-    <t xml:space="preserve">Self-tapping screws M2/M3, 6-12 mm (≈14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 machine screws (wrist and pinion clamps)</t>
+    <t xml:space="preserve">M3 large washers Ø9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 washers Ø7 (MG996R tab screws)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-tapping screws M2-M3, 6-12 mm (≈33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab, cover, ring, cradle and horn screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 × 12 machine screws (wrist and pinion clamps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 washers Ø6</t>
   </si>
   <si>
     <t xml:space="preserve">#4 × 2 in wood screws (desk mounting)</t>
   </si>
   <si>
+    <t xml:space="preserve">Or a 200 × 200 mm board with rubber feet</t>
+  </si>
+  <si>
     <t xml:space="preserve">1/4"-20 × 5/16" thumb screw (camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">Deep review 01-S6</t>
+    <t xml:space="preserve">Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTFE tape (turntable ring)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubber feet (board option)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA glue (horn in the pinion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG filament (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest slices (arm links round 3, claw round 1); the arm round will change them. 'Cost to buy' counts whole 1 kg spools.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Print electricity (hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printer power × NB Power rate (Summary sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rover: bought parts and print cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motors and boards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N20 gearmotor 6 V ≈150:1 (LP or MP), 3 mm D-shaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pololu #1996 aluminium hub, 3 mm (2-pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB6612FNG motor driver carrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC-SR04 ultrasonic sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170-point mini breadboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18650 Li-ion cells, protected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 × 18650 series holder (long)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-bay Li-ion charger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP1584 buck module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTS-102 mini toggle switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 µF electrolytic capacitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 nF ceramic capacitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schottky diode (SS14 / 1N5817 / 1N5818)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistors (1k, 2k, 33k, 100k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 kΩ resistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The kit has no 33k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumper wires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 AWG silicone wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velcro battery strap 20 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 50 socket head, class 12.9, fully threaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not stainless A2-70 (strength round 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 40 socket head, class 12.9, fully threaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 12 and M3 × 8 socket head, M3 nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 20 set screw, flat point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 hex nuts DIN 934 (wall nut traps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø2 mm steel rod, 100 mm (cut into 68 + 2 track pins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or buy Ø2 × 24 dowel pins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 mm steel flat bar (idler plates, round 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut two plates of each size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double-sided mounting tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threadlocker, medium (blue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round-2 slices; round 3 not sliced yet. 'Cost to buy' counts whole 1 kg spools.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexapod: bought parts and print cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG90S metal-gear micro servo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCA9685 16-channel servo driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2S 1000 mAh LiPo, ≥ 20C, XT30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBEC, 2S input, 6 V, ≥ 5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch rated ≥ 10 A DC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inline blade-fuse holder + 7.5 A blade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT30 male pigtail, 18 AWG (mates with the LiPo's female plug)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price is for the same pigtail with the other gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiPo voltage alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiPo charging bag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 µF electrolytic capacitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 nF ceramic capacitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schottky diode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistors (33k, 100k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 femur + 6 tibia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip ties (≤ 2.5 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 machine screws 12-14 mm (clamps and coxa tabs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 Nyloc nuts (coxa tabs, round 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2 washers Ø5 and Ø6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 penny washers Ø9-10 (coxa clamps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-tapping screws M2 8-10 mm and M3 × 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2.5 × 6 self-tapping (PCA9685 boards)</t>
   </si>
   <si>
     <t xml:space="preserve">M1.7 × 5 horn anti-rotation screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep review 01-S4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTFE tape (turntable ring)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deep review 03-SYS-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA glue (horn in the pinion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG filament (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latest slices (arm links round 3, claw round 1); the arm round will change them. 'Cost to buy' counts whole 1 kg spools.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Print electricity (hours)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printer power × NB Power rate (Summary sheet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rover: bought parts and print cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motors and boards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N20 gearmotor 6 V ≈150:1 (LP or MP), 3 mm D-shaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pololu #1996 aluminium hub, 3 mm (2-pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB6612FNG motor driver carrier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HC-SR04 ultrasonic sensor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170-point mini breadboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18650 Li-ion cells, protected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 × 18650 series holder (long)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two-bay Li-ion charger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP1584 buck module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTS-102 mini toggle switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 µF electrolytic capacitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 nF ceramic capacitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schottky diode (SS14 / 1N5817 / 1N5818)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resistors (1k, 2k, 33k, 100k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33 kΩ resistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The kit has no 33k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumper wires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 AWG silicone wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velcro battery strap 20 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 50 socket head, class 12.9, fully threaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not stainless A2-70 (strength round 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 40 socket head, class 12.9, fully threaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 12 and M3 × 8 socket head, M3 nuts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 20 set screw, flat point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 hex nuts DIN 934 (wall nut traps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ø2 mm steel rod, 100 mm (cut into 68 + 2 track pins)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or buy Ø2 × 24 dowel pins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 mm steel flat bar (idler plates, round 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut two plates of each size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Double-sided mounting tape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of a roll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threadlocker, medium (blue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of a bottle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round-2 slices; round 3 not sliced yet. 'Cost to buy' counts whole 1 kg spools.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexapod: bought parts and print cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG90S metal-gear micro servo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCA9685 16-channel servo driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2S 1000 mAh LiPo, ≥ 20C, XT30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBEC, 2S input, 6 V, ≥ 5 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch rated ≥ 10 A DC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inline blade-fuse holder + 7.5 A blade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XT30 male pigtail, 18 AWG (mates with the LiPo's female plug)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price is for the same pigtail with the other gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiPo voltage alarm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiPo charging bag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000 µF electrolytic capacitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 nF ceramic capacitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schottky diode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resistors (33k, 100k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 femur + 6 tibia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zip ties (≤ 2.5 mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 machine screws 12-14 mm (clamps and coxa tabs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 Nyloc nuts (coxa tabs, round 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2 washers Ø5 and Ø6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 penny washers Ø9-10 (coxa clamps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-tapping screws M2 8-10 mm and M3 × 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2.5 × 6 self-tapping (PCA9685 boards)</t>
   </si>
   <si>
     <t xml:space="preserve">Estimate: strength round-3 mass model and the round-4 print-time estimates. 'Cost to buy' counts whole 1 kg spools.</t>
@@ -2206,28 +2269,28 @@
         <v>21</v>
       </c>
       <c r="C15" s="12" t="n">
-        <f aca="false">SUM(Arm!J5:J32)</f>
-        <v>235.39</v>
+        <f aca="false">SUM(Arm!J5:J36)</f>
+        <v>243.16</v>
       </c>
       <c r="D15" s="12" t="n">
-        <f aca="false">Arm!J35</f>
+        <f aca="false">Arm!J39</f>
         <v>14.99</v>
       </c>
       <c r="E15" s="8" t="n">
-        <f aca="false">Arm!J36</f>
+        <f aca="false">Arm!J40</f>
         <v>0.4305312</v>
       </c>
       <c r="F15" s="13" t="n">
         <f aca="false">SUM(C15:E15)</f>
-        <v>250.8105312</v>
+        <v>258.5805312</v>
       </c>
       <c r="G15" s="14" t="n">
         <f aca="false">F15*(1+$C$7)</f>
-        <v>288.43211088</v>
+        <v>297.36761088</v>
       </c>
       <c r="H15" s="13" t="n">
-        <f aca="false">Arm!K38*(1+$C$7)</f>
-        <v>263.69676203</v>
+        <f aca="false">Arm!K42*(1+$C$7)</f>
+        <v>272.63226203</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2293,28 +2356,28 @@
         <v>24</v>
       </c>
       <c r="C18" s="16" t="n">
-        <f aca="false">SUM('All three'!G5:G73)</f>
-        <v>757.59414</v>
+        <f aca="false">SUM('All three'!G5:G76)</f>
+        <v>766.41414</v>
       </c>
       <c r="D18" s="16" t="n">
-        <f aca="false">'All three'!G75</f>
+        <f aca="false">'All three'!G78</f>
         <v>29.98</v>
       </c>
       <c r="E18" s="17" t="n">
-        <f aca="false">'All three'!G76</f>
+        <f aca="false">'All three'!G79</f>
         <v>1.3486176</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">SUM(C18:E18)</f>
-        <v>788.9227576</v>
+        <v>797.7427576</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">F18*(1+$C$7)</f>
-        <v>907.26117124</v>
+        <v>917.40417124</v>
       </c>
       <c r="H18" s="18" t="n">
-        <f aca="false">'All three'!H78*(1+$C$7)</f>
-        <v>791.03240199</v>
+        <f aca="false">'All three'!H81*(1+$C$7)</f>
+        <v>801.17540199</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2323,7 +2386,7 @@
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">SUM(G15:G17)-G18</f>
-        <v>223.44424215</v>
+        <v>222.23674215</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2358,24 +2421,24 @@
         <v>21</v>
       </c>
       <c r="C23" s="12" t="n">
-        <f aca="false">SUM(Arm!F5:F32)</f>
-        <v>147.869</v>
+        <f aca="false">SUM(Arm!F5:F36)</f>
+        <v>152.09</v>
       </c>
       <c r="D23" s="12" t="n">
-        <f aca="false">Arm!F35</f>
+        <f aca="false">Arm!F39</f>
         <v>4.9467</v>
       </c>
       <c r="E23" s="8" t="n">
-        <f aca="false">Arm!F36</f>
+        <f aca="false">Arm!F40</f>
         <v>0.4305312</v>
       </c>
       <c r="F23" s="13" t="n">
         <f aca="false">SUM(C23:E23)</f>
-        <v>153.2462312</v>
+        <v>157.4672312</v>
       </c>
       <c r="G23" s="13" t="n">
         <f aca="false">F23*(1+$C$7)</f>
-        <v>176.23316588</v>
+        <v>181.08731588</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2507,7 +2570,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -5094,7 +5157,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="20" t="s">
         <v>325</v>
       </c>
@@ -5105,33 +5168,33 @@
         <v>327</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="E67" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="23" t="n">
-        <v>3.99</v>
+        <v>6</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H67" s="24" t="n">
         <f aca="false">IF(G67="USD",F67*Summary!$C$8,F67)</f>
-        <v>3.99</v>
+        <v>6</v>
       </c>
       <c r="I67" s="24" t="n">
         <f aca="false">H67/E67</f>
-        <v>3.99</v>
+        <v>6</v>
       </c>
       <c r="J67" s="25"/>
       <c r="K67" s="26"/>
       <c r="L67" s="26"/>
       <c r="M67" s="20" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="N67" s="21" t="s">
-        <v>328</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5145,24 +5208,24 @@
         <v>331</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>146</v>
+        <v>53</v>
       </c>
       <c r="E68" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="23" t="n">
-        <v>7.07</v>
+        <v>3.99</v>
       </c>
       <c r="G68" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H68" s="24" t="n">
         <f aca="false">IF(G68="USD",F68*Summary!$C$8,F68)</f>
-        <v>7.07</v>
+        <v>3.99</v>
       </c>
       <c r="I68" s="24" t="n">
         <f aca="false">H68/E68</f>
-        <v>7.07</v>
+        <v>3.99</v>
       </c>
       <c r="J68" s="25"/>
       <c r="K68" s="26"/>
@@ -5174,7 +5237,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="20" t="s">
         <v>333</v>
       </c>
@@ -5185,36 +5248,36 @@
         <v>335</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>336</v>
+        <v>146</v>
       </c>
       <c r="E69" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="23" t="n">
-        <v>3</v>
+        <v>7.07</v>
       </c>
       <c r="G69" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H69" s="24" t="n">
         <f aca="false">IF(G69="USD",F69*Summary!$C$8,F69)</f>
-        <v>3</v>
+        <v>7.07</v>
       </c>
       <c r="I69" s="24" t="n">
         <f aca="false">H69/E69</f>
-        <v>3</v>
+        <v>7.07</v>
       </c>
       <c r="J69" s="25"/>
       <c r="K69" s="26"/>
       <c r="L69" s="26"/>
       <c r="M69" s="20" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="N69" s="21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="20" t="s">
         <v>337</v>
       </c>
@@ -5225,36 +5288,36 @@
         <v>339</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>53</v>
+        <v>340</v>
       </c>
       <c r="E70" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="23" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="G70" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H70" s="24" t="n">
         <f aca="false">IF(G70="USD",F70*Summary!$C$8,F70)</f>
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="I70" s="24" t="n">
         <f aca="false">H70/E70</f>
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="J70" s="25"/>
       <c r="K70" s="26"/>
       <c r="L70" s="26"/>
       <c r="M70" s="20" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="N70" s="21" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="20" t="s">
         <v>341</v>
       </c>
@@ -5265,64 +5328,64 @@
         <v>343</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F71" s="23" t="n">
-        <v>0.72</v>
+        <v>4</v>
       </c>
       <c r="G71" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H71" s="24" t="n">
         <f aca="false">IF(G71="USD",F71*Summary!$C$8,F71)</f>
-        <v>0.72</v>
+        <v>4</v>
       </c>
       <c r="I71" s="24" t="n">
         <f aca="false">H71/E71</f>
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="J71" s="25"/>
       <c r="K71" s="26"/>
       <c r="L71" s="26"/>
       <c r="M71" s="20" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="N71" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="B72" s="20" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="s">
+      <c r="C72" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="B72" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>348</v>
-      </c>
       <c r="D72" s="21" t="s">
-        <v>349</v>
+        <v>53</v>
       </c>
       <c r="E72" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="23" t="n">
-        <v>24.99</v>
+        <v>2.29</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="H72" s="24" t="n">
         <f aca="false">IF(G72="USD",F72*Summary!$C$8,F72)</f>
-        <v>34.968507</v>
+        <v>2.29</v>
       </c>
       <c r="I72" s="24" t="n">
         <f aca="false">H72/E72</f>
-        <v>34.968507</v>
+        <v>2.29</v>
       </c>
       <c r="J72" s="25"/>
       <c r="K72" s="26"/>
@@ -5331,38 +5394,38 @@
         <v>55</v>
       </c>
       <c r="N72" s="21" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="C73" s="21" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20" t="s">
+      <c r="D73" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="B73" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>65</v>
-      </c>
       <c r="E73" s="22" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="23" t="n">
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="G73" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H73" s="24" t="n">
         <f aca="false">IF(G73="USD",F73*Summary!$C$8,F73)</f>
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="I73" s="24" t="n">
         <f aca="false">H73/E73</f>
-        <v>15</v>
+        <v>0.72</v>
       </c>
       <c r="J73" s="25"/>
       <c r="K73" s="26"/>
@@ -5371,38 +5434,38 @@
         <v>55</v>
       </c>
       <c r="N73" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B74" s="20" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20" t="s">
+      <c r="C74" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="B74" s="20" t="s">
+      <c r="D74" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="C74" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>180</v>
-      </c>
       <c r="E74" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="23" t="n">
-        <v>6.42</v>
+        <v>24.99</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>86</v>
       </c>
       <c r="H74" s="24" t="n">
         <f aca="false">IF(G74="USD",F74*Summary!$C$8,F74)</f>
-        <v>8.983506</v>
+        <v>34.968507</v>
       </c>
       <c r="I74" s="24" t="n">
         <f aca="false">H74/E74</f>
-        <v>4.491753</v>
+        <v>34.968507</v>
       </c>
       <c r="J74" s="25"/>
       <c r="K74" s="26"/>
@@ -5411,18 +5474,18 @@
         <v>55</v>
       </c>
       <c r="N74" s="21" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="20" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20" t="s">
+      <c r="B75" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="C75" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="D75" s="21" t="s">
         <v>65</v>
@@ -5431,18 +5494,18 @@
         <v>1</v>
       </c>
       <c r="F75" s="23" t="n">
-        <v>19.93</v>
+        <v>15</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H75" s="24" t="n">
         <f aca="false">IF(G75="USD",F75*Summary!$C$8,F75)</f>
-        <v>19.93</v>
+        <v>15</v>
       </c>
       <c r="I75" s="24" t="n">
         <f aca="false">H75/E75</f>
-        <v>19.93</v>
+        <v>15</v>
       </c>
       <c r="J75" s="25"/>
       <c r="K75" s="26"/>
@@ -5451,38 +5514,38 @@
         <v>55</v>
       </c>
       <c r="N75" s="21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20" t="s">
+      <c r="B76" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="C76" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="C76" s="21" t="s">
-        <v>365</v>
-      </c>
       <c r="D76" s="21" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F76" s="23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G76" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H76" s="24" t="n">
         <f aca="false">IF(G76="USD",F76*Summary!$C$8,F76)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I76" s="24" t="n">
         <f aca="false">H76/E76</f>
-        <v>0.16</v>
+        <v>8</v>
       </c>
       <c r="J76" s="25"/>
       <c r="K76" s="26"/>
@@ -5491,87 +5554,247 @@
         <v>132</v>
       </c>
       <c r="N76" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="C77" s="21" t="s">
         <v>367</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="B77" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>370</v>
       </c>
       <c r="D77" s="21" t="s">
         <v>180</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>1.98</v>
+        <v>6.42</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>86</v>
       </c>
       <c r="H77" s="24" t="n">
         <f aca="false">IF(G77="USD",F77*Summary!$C$8,F77)</f>
-        <v>2.770614</v>
+        <v>8.983506</v>
       </c>
       <c r="I77" s="24" t="n">
         <f aca="false">H77/E77</f>
-        <v>2.770614</v>
+        <v>4.491753</v>
       </c>
       <c r="J77" s="25"/>
       <c r="K77" s="26"/>
       <c r="L77" s="26"/>
       <c r="M77" s="20" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="N77" s="21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="C78" s="21" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>374</v>
-      </c>
       <c r="D78" s="21" t="s">
-        <v>91</v>
+        <v>328</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F78" s="23" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>54</v>
       </c>
       <c r="H78" s="24" t="n">
         <f aca="false">IF(G78="USD",F78*Summary!$C$8,F78)</f>
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="I78" s="24" t="n">
         <f aca="false">H78/E78</f>
-        <v>0.0599</v>
+        <v>6</v>
       </c>
       <c r="J78" s="25"/>
       <c r="K78" s="26"/>
       <c r="L78" s="26"/>
       <c r="M78" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="N78" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="23" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="G79" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H79" s="24" t="n">
+        <f aca="false">IF(G79="USD",F79*Summary!$C$8,F79)</f>
+        <v>19.93</v>
+      </c>
+      <c r="I79" s="24" t="n">
+        <f aca="false">H79/E79</f>
+        <v>19.93</v>
+      </c>
+      <c r="J79" s="25"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="21" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H80" s="24" t="n">
+        <f aca="false">IF(G80="USD",F80*Summary!$C$8,F80)</f>
+        <v>4</v>
+      </c>
+      <c r="I80" s="24" t="n">
+        <f aca="false">H80/E80</f>
+        <v>0.16</v>
+      </c>
+      <c r="J80" s="25"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="N80" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G81" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="H81" s="24" t="n">
+        <f aca="false">IF(G81="USD",F81*Summary!$C$8,F81)</f>
+        <v>2.770614</v>
+      </c>
+      <c r="I81" s="24" t="n">
+        <f aca="false">H81/E81</f>
+        <v>2.770614</v>
+      </c>
+      <c r="J81" s="25"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="N78" s="21" t="s">
-        <v>375</v>
+      <c r="N81" s="21" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F82" s="23" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H82" s="24" t="n">
+        <f aca="false">IF(G82="USD",F82*Summary!$C$8,F82)</f>
+        <v>5.99</v>
+      </c>
+      <c r="I82" s="24" t="n">
+        <f aca="false">H82/E82</f>
+        <v>0.0599</v>
+      </c>
+      <c r="J82" s="25"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="N82" s="21" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5816,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -5610,12 +5833,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5631,48 +5854,48 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>40</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>41</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>252</v>
@@ -5681,7 +5904,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>8.95</v>
       </c>
       <c r="F5" s="24" t="n">
@@ -5689,7 +5912,7 @@
         <v>26.85</v>
       </c>
       <c r="G5" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H5" s="20" t="n">
@@ -5697,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>8.95</v>
       </c>
       <c r="J5" s="24" t="n">
@@ -5705,17 +5928,19 @@
         <v>26.85</v>
       </c>
       <c r="K5" s="24" t="n">
-        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0))),CEILING(D5/INDEX(Prices!$K$5:$K$78,MATCH(C5,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0)),J5))</f>
+        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0))),CEILING(D5/INDEX(Prices!$K$5:$K$82,MATCH(C5,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0)),J5))</f>
         <v>20.947521</v>
       </c>
-      <c r="L5" s="21"/>
+      <c r="L5" s="21" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>247</v>
@@ -5724,7 +5949,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>6</v>
       </c>
       <c r="F6" s="24" t="n">
@@ -5732,7 +5957,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H6" s="20" t="n">
@@ -5740,7 +5965,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>6</v>
       </c>
       <c r="J6" s="24" t="n">
@@ -5748,17 +5973,17 @@
         <v>12</v>
       </c>
       <c r="K6" s="24" t="n">
-        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0))),CEILING(D6/INDEX(Prices!$K$5:$K$78,MATCH(C6,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0)),J6))</f>
+        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0))),CEILING(D6/INDEX(Prices!$K$5:$K$82,MATCH(C6,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0)),J6))</f>
         <v>6.43678</v>
       </c>
       <c r="L6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>123</v>
@@ -5767,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="F7" s="24" t="n">
@@ -5775,7 +6000,7 @@
         <v>9.86</v>
       </c>
       <c r="G7" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H7" s="20" t="n">
@@ -5783,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="J7" s="24" t="n">
@@ -5791,17 +6016,17 @@
         <v>9.86</v>
       </c>
       <c r="K7" s="24" t="n">
-        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0))),CEILING(D7/INDEX(Prices!$K$5:$K$78,MATCH(C7,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0)),J7))</f>
+        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0))),CEILING(D7/INDEX(Prices!$K$5:$K$82,MATCH(C7,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0)),J7))</f>
         <v>9.86</v>
       </c>
       <c r="L7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>57</v>
@@ -5810,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>249.99</v>
       </c>
       <c r="F8" s="24" t="n">
@@ -5818,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H8" s="20" t="n">
@@ -5826,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>249.99</v>
       </c>
       <c r="J8" s="24" t="n">
@@ -5834,19 +6059,19 @@
         <v>0</v>
       </c>
       <c r="K8" s="24" t="n">
-        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0))),CEILING(D8/INDEX(Prices!$K$5:$K$78,MATCH(C8,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0)),J8))</f>
+        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0))),CEILING(D8/INDEX(Prices!$K$5:$K$82,MATCH(C8,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0)),J8))</f>
         <v>0</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>285</v>
@@ -5855,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>27.13</v>
       </c>
       <c r="F9" s="24" t="n">
@@ -5863,7 +6088,7 @@
         <v>27.13</v>
       </c>
       <c r="G9" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H9" s="20" t="n">
@@ -5871,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>27.13</v>
       </c>
       <c r="J9" s="24" t="n">
@@ -5879,17 +6104,17 @@
         <v>27.13</v>
       </c>
       <c r="K9" s="24" t="n">
-        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0))),CEILING(D9/INDEX(Prices!$K$5:$K$78,MATCH(C9,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0)),J9))</f>
+        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0))),CEILING(D9/INDEX(Prices!$K$5:$K$82,MATCH(C9,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0)),J9))</f>
         <v>27.13</v>
       </c>
       <c r="L9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>105</v>
@@ -5898,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="F10" s="24" t="n">
@@ -5906,7 +6131,7 @@
         <v>1.95</v>
       </c>
       <c r="G10" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H10" s="20" t="n">
@@ -5914,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="J10" s="24" t="n">
@@ -5922,17 +6147,17 @@
         <v>1.95</v>
       </c>
       <c r="K10" s="24" t="n">
-        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0))),CEILING(D10/INDEX(Prices!$K$5:$K$78,MATCH(C10,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0)),J10))</f>
+        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0))),CEILING(D10/INDEX(Prices!$K$5:$K$82,MATCH(C10,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0)),J10))</f>
         <v>1.95</v>
       </c>
       <c r="L10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>110</v>
@@ -5941,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>4.95</v>
       </c>
       <c r="F11" s="24" t="n">
@@ -5949,7 +6174,7 @@
         <v>4.95</v>
       </c>
       <c r="G11" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H11" s="20" t="n">
@@ -5957,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>4.95</v>
       </c>
       <c r="J11" s="24" t="n">
@@ -5965,17 +6190,17 @@
         <v>4.95</v>
       </c>
       <c r="K11" s="24" t="n">
-        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0))),CEILING(D11/INDEX(Prices!$K$5:$K$78,MATCH(C11,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0)),J11))</f>
+        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0))),CEILING(D11/INDEX(Prices!$K$5:$K$82,MATCH(C11,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0)),J11))</f>
         <v>4.95</v>
       </c>
       <c r="L11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>134</v>
@@ -5984,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>6.945</v>
       </c>
       <c r="F12" s="24" t="n">
@@ -5992,7 +6217,7 @@
         <v>6.945</v>
       </c>
       <c r="G12" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="H12" s="20" t="n">
@@ -6000,7 +6225,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>13.89</v>
       </c>
       <c r="J12" s="24" t="n">
@@ -6008,34 +6233,34 @@
         <v>13.89</v>
       </c>
       <c r="K12" s="24" t="n">
-        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0))),CEILING(D12/INDEX(Prices!$K$5:$K$78,MATCH(C12,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0)),J12))</f>
+        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0))),CEILING(D12/INDEX(Prices!$K$5:$K$82,MATCH(C12,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0)),J12))</f>
         <v>13.89</v>
       </c>
       <c r="L12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
-        <v>18.16</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="F13" s="24" t="n">
         <f aca="false">D13*E13</f>
-        <v>18.16</v>
+        <v>6</v>
       </c>
       <c r="G13" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H13" s="20" t="n">
@@ -6043,44 +6268,44 @@
         <v>1</v>
       </c>
       <c r="I13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
-        <v>18.16</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="J13" s="24" t="n">
         <f aca="false">H13*I13</f>
-        <v>18.16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="24" t="n">
-        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0))),CEILING(D13/INDEX(Prices!$K$5:$K$78,MATCH(C13,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0)),J13))</f>
-        <v>18.16</v>
+        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0))),CEILING(D13/INDEX(Prices!$K$5:$K$82,MATCH(C13,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0)),J13))</f>
+        <v>6</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>62</v>
+        <v>369</v>
       </c>
       <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
-        <v>0.71</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="F14" s="24" t="n">
         <f aca="false">D14*E14</f>
-        <v>0.71</v>
+        <v>6</v>
       </c>
       <c r="G14" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H14" s="20" t="n">
@@ -6088,42 +6313,44 @@
         <v>1</v>
       </c>
       <c r="I14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
-        <v>0.71</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="J14" s="24" t="n">
         <f aca="false">H14*I14</f>
-        <v>0.71</v>
+        <v>6</v>
       </c>
       <c r="K14" s="24" t="n">
-        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0))),CEILING(D14/INDEX(Prices!$K$5:$K$78,MATCH(C14,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0)),J14))</f>
-        <v>0.71</v>
-      </c>
-      <c r="L14" s="21"/>
+        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0))),CEILING(D14/INDEX(Prices!$K$5:$K$82,MATCH(C14,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0)),J14))</f>
+        <v>6</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>341</v>
+        <v>62</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
-        <v>0.72</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
+        <v>0.71</v>
       </c>
       <c r="F15" s="24" t="n">
         <f aca="false">D15*E15</f>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G15" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H15" s="20" t="n">
@@ -6131,222 +6358,218 @@
         <v>1</v>
       </c>
       <c r="I15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
-        <v>0.72</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
+        <v>0.71</v>
       </c>
       <c r="J15" s="24" t="n">
         <f aca="false">H15*I15</f>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K15" s="24" t="n">
-        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0))),CEILING(D15/INDEX(Prices!$K$5:$K$78,MATCH(C15,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0)),J15))</f>
-        <v>0.72</v>
-      </c>
-      <c r="L15" s="21" t="s">
-        <v>402</v>
-      </c>
+        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0))),CEILING(D15/INDEX(Prices!$K$5:$K$82,MATCH(C15,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0)),J15))</f>
+        <v>0.71</v>
+      </c>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
-        <v>1.36</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
+        <v>0.72</v>
       </c>
       <c r="F16" s="24" t="n">
         <f aca="false">D16*E16</f>
-        <v>2.72</v>
+        <v>0.72</v>
       </c>
       <c r="G16" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H16" s="20" t="n">
         <f aca="false">IF(D16&lt;=0,0,CEILING(D16/G16,1))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
-        <v>1.36</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
+        <v>0.72</v>
       </c>
       <c r="J16" s="24" t="n">
         <f aca="false">H16*I16</f>
-        <v>2.72</v>
+        <v>0.72</v>
       </c>
       <c r="K16" s="24" t="n">
-        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0))),CEILING(D16/INDEX(Prices!$K$5:$K$78,MATCH(C16,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0)),J16))</f>
-        <v>2.72</v>
+        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0))),CEILING(D16/INDEX(Prices!$K$5:$K$82,MATCH(C16,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0)),J16))</f>
+        <v>0.72</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D17" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
-        <v>3.06</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
+        <v>1.36</v>
       </c>
       <c r="F17" s="24" t="n">
         <f aca="false">D17*E17</f>
-        <v>3.06</v>
+        <v>2.72</v>
       </c>
       <c r="G17" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H17" s="20" t="n">
         <f aca="false">IF(D17&lt;=0,0,CEILING(D17/G17,1))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
-        <v>3.06</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
+        <v>1.36</v>
       </c>
       <c r="J17" s="24" t="n">
         <f aca="false">H17*I17</f>
-        <v>3.06</v>
+        <v>2.72</v>
       </c>
       <c r="K17" s="24" t="n">
-        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0))),CEILING(D17/INDEX(Prices!$K$5:$K$78,MATCH(C17,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0)),J17))</f>
-        <v>3.06</v>
+        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0))),CEILING(D17/INDEX(Prices!$K$5:$K$82,MATCH(C17,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0)),J17))</f>
+        <v>2.72</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>165</v>
+        <v>317</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
-        <v>0.1425</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
+        <v>3.06</v>
       </c>
       <c r="F18" s="24" t="n">
         <f aca="false">D18*E18</f>
-        <v>2.1375</v>
+        <v>3.06</v>
       </c>
       <c r="G18" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
-        <v>40</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="H18" s="20" t="n">
         <f aca="false">IF(D18&lt;=0,0,CEILING(D18/G18,1))</f>
         <v>1</v>
       </c>
       <c r="I18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
-        <v>5.7</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
+        <v>3.06</v>
       </c>
       <c r="J18" s="24" t="n">
         <f aca="false">H18*I18</f>
-        <v>5.7</v>
+        <v>3.06</v>
       </c>
       <c r="K18" s="24" t="n">
-        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0))),CEILING(D18/INDEX(Prices!$K$5:$K$78,MATCH(C18,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0)),J18))</f>
-        <v>5.7</v>
+        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0))),CEILING(D18/INDEX(Prices!$K$5:$K$82,MATCH(C18,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0)),J18))</f>
+        <v>3.06</v>
       </c>
       <c r="L18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="E19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
-        <v>12.95</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
+        <v>0.1425</v>
       </c>
       <c r="F19" s="24" t="n">
         <f aca="false">D19*E19</f>
-        <v>1.295</v>
+        <v>0.7125</v>
       </c>
       <c r="G19" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
+        <v>40</v>
       </c>
       <c r="H19" s="20" t="n">
         <f aca="false">IF(D19&lt;=0,0,CEILING(D19/G19,1))</f>
         <v>1</v>
       </c>
       <c r="I19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
-        <v>12.95</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
+        <v>5.7</v>
       </c>
       <c r="J19" s="24" t="n">
         <f aca="false">H19*I19</f>
-        <v>12.95</v>
+        <v>5.7</v>
       </c>
       <c r="K19" s="24" t="n">
-        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0))),CEILING(D19/INDEX(Prices!$K$5:$K$78,MATCH(C19,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0)),J19))</f>
-        <v>12.95</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>410</v>
-      </c>
+        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0))),CEILING(D19/INDEX(Prices!$K$5:$K$82,MATCH(C19,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0)),J19))</f>
+        <v>5.7</v>
+      </c>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
-        <v>15</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
+        <v>12.95</v>
       </c>
       <c r="F20" s="24" t="n">
         <f aca="false">D20*E20</f>
-        <v>15</v>
+        <v>1.295</v>
       </c>
       <c r="G20" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H20" s="20" t="n">
@@ -6354,87 +6577,87 @@
         <v>1</v>
       </c>
       <c r="I20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
-        <v>15</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
+        <v>12.95</v>
       </c>
       <c r="J20" s="24" t="n">
         <f aca="false">H20*I20</f>
-        <v>15</v>
+        <v>12.95</v>
       </c>
       <c r="K20" s="24" t="n">
-        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0))),CEILING(D20/INDEX(Prices!$K$5:$K$78,MATCH(C20,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0)),J20))</f>
-        <v>15</v>
+        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0))),CEILING(D20/INDEX(Prices!$K$5:$K$82,MATCH(C20,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0)),J20))</f>
+        <v>12.95</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
-        <v>0.0599</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
+        <v>8</v>
       </c>
       <c r="F21" s="24" t="n">
         <f aca="false">D21*E21</f>
-        <v>0.599</v>
+        <v>8</v>
       </c>
       <c r="G21" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
-        <v>100</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="H21" s="20" t="n">
         <f aca="false">IF(D21&lt;=0,0,CEILING(D21/G21,1))</f>
         <v>1</v>
       </c>
       <c r="I21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
-        <v>5.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
+        <v>8</v>
       </c>
       <c r="J21" s="24" t="n">
         <f aca="false">H21*I21</f>
-        <v>5.99</v>
+        <v>8</v>
       </c>
       <c r="K21" s="24" t="n">
-        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0))),CEILING(D21/INDEX(Prices!$K$5:$K$78,MATCH(C21,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0)),J21))</f>
-        <v>5.99</v>
+        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0))),CEILING(D21/INDEX(Prices!$K$5:$K$82,MATCH(C21,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0)),J21))</f>
+        <v>8</v>
       </c>
       <c r="L21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>148</v>
+        <v>358</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
-        <v>12.84</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
+        <v>15</v>
       </c>
       <c r="F22" s="24" t="n">
         <f aca="false">D22*E22</f>
-        <v>1.284</v>
+        <v>15</v>
       </c>
       <c r="G22" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H22" s="20" t="n">
@@ -6442,573 +6665,745 @@
         <v>1</v>
       </c>
       <c r="I22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
-        <v>12.84</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
+        <v>15</v>
       </c>
       <c r="J22" s="24" t="n">
         <f aca="false">H22*I22</f>
-        <v>12.84</v>
+        <v>15</v>
       </c>
       <c r="K22" s="24" t="n">
-        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0))),CEILING(D22/INDEX(Prices!$K$5:$K$78,MATCH(C22,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0)),J22))</f>
-        <v>12.84</v>
+        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0))),CEILING(D22/INDEX(Prices!$K$5:$K$82,MATCH(C22,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0)),J22))</f>
+        <v>15</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>236</v>
+        <v>385</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="E23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
-        <v>24</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
+        <v>0.0599</v>
       </c>
       <c r="F23" s="24" t="n">
         <f aca="false">D23*E23</f>
-        <v>1.2</v>
+        <v>0.599</v>
       </c>
       <c r="G23" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
+        <v>100</v>
       </c>
       <c r="H23" s="20" t="n">
         <f aca="false">IF(D23&lt;=0,0,CEILING(D23/G23,1))</f>
         <v>1</v>
       </c>
       <c r="I23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
-        <v>24</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
+        <v>5.99</v>
       </c>
       <c r="J23" s="24" t="n">
         <f aca="false">H23*I23</f>
-        <v>24</v>
+        <v>5.99</v>
       </c>
       <c r="K23" s="24" t="n">
-        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0))),CEILING(D23/INDEX(Prices!$K$5:$K$78,MATCH(C23,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0)),J23))</f>
-        <v>24</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>417</v>
-      </c>
+        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0))),CEILING(D23/INDEX(Prices!$K$5:$K$82,MATCH(C23,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0)),J23))</f>
+        <v>5.99</v>
+      </c>
+      <c r="L23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>241</v>
+        <v>430</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
-        <v>0.1</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
+        <v>0.4</v>
       </c>
       <c r="F24" s="24" t="n">
         <f aca="false">D24*E24</f>
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="G24" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
-        <v>50</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
+        <v>10</v>
       </c>
       <c r="H24" s="20" t="n">
         <f aca="false">IF(D24&lt;=0,0,CEILING(D24/G24,1))</f>
         <v>1</v>
       </c>
       <c r="I24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
-        <v>5</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
       </c>
       <c r="J24" s="24" t="n">
         <f aca="false">H24*I24</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="24" t="n">
-        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0))),CEILING(D24/INDEX(Prices!$K$5:$K$78,MATCH(C24,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0)),J24))</f>
-        <v>5</v>
+        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0))),CEILING(D24/INDEX(Prices!$K$5:$K$82,MATCH(C24,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0)),J24))</f>
+        <v>4</v>
       </c>
       <c r="L24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>14</v>
+        <v>0.1</v>
       </c>
       <c r="E25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
-        <v>0.149</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
+        <v>12.84</v>
       </c>
       <c r="F25" s="24" t="n">
         <f aca="false">D25*E25</f>
-        <v>2.086</v>
+        <v>1.284</v>
       </c>
       <c r="G25" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
-        <v>10</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="H25" s="20" t="n">
         <f aca="false">IF(D25&lt;=0,0,CEILING(D25/G25,1))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
-        <v>1.49</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
+        <v>12.84</v>
       </c>
       <c r="J25" s="24" t="n">
         <f aca="false">H25*I25</f>
-        <v>2.98</v>
+        <v>12.84</v>
       </c>
       <c r="K25" s="24" t="n">
-        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0))),CEILING(D25/INDEX(Prices!$K$5:$K$78,MATCH(C25,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0)),J25))</f>
-        <v>2.98</v>
-      </c>
-      <c r="L25" s="21"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0))),CEILING(D25/INDEX(Prices!$K$5:$K$82,MATCH(C25,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0)),J25))</f>
+        <v>12.84</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="D26" s="22" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="E26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
-        <v>0.1475</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
+        <v>24</v>
       </c>
       <c r="F26" s="24" t="n">
         <f aca="false">D26*E26</f>
-        <v>0.295</v>
+        <v>1.2</v>
       </c>
       <c r="G26" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
-        <v>20</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="H26" s="20" t="n">
         <f aca="false">IF(D26&lt;=0,0,CEILING(D26/G26,1))</f>
         <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
-        <v>2.95</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
+        <v>24</v>
       </c>
       <c r="J26" s="24" t="n">
         <f aca="false">H26*I26</f>
-        <v>2.95</v>
+        <v>24</v>
       </c>
       <c r="K26" s="24" t="n">
-        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0))),CEILING(D26/INDEX(Prices!$K$5:$K$78,MATCH(C26,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0)),J26))</f>
-        <v>2.95</v>
-      </c>
-      <c r="L26" s="21"/>
+        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0))),CEILING(D26/INDEX(Prices!$K$5:$K$82,MATCH(C26,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0)),J26))</f>
+        <v>24</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>363</v>
+        <v>240</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
-        <v>0.16</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
+        <v>0.1</v>
       </c>
       <c r="F27" s="24" t="n">
         <f aca="false">D27*E27</f>
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
-        <v>25</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
+        <v>50</v>
       </c>
       <c r="H27" s="20" t="n">
         <f aca="false">IF(D27&lt;=0,0,CEILING(D27/G27,1))</f>
         <v>1</v>
       </c>
       <c r="I27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
-        <v>4</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
+        <v>5</v>
       </c>
       <c r="J27" s="24" t="n">
         <f aca="false">H27*I27</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="24" t="n">
-        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0))),CEILING(D27/INDEX(Prices!$K$5:$K$78,MATCH(C27,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0)),J27))</f>
-        <v>4</v>
+        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0))),CEILING(D27/INDEX(Prices!$K$5:$K$82,MATCH(C27,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0)),J27))</f>
+        <v>5</v>
       </c>
       <c r="L27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
-        <v>3</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
+        <v>0.04875</v>
       </c>
       <c r="F28" s="24" t="n">
         <f aca="false">D28*E28</f>
-        <v>3</v>
+        <v>0.585</v>
       </c>
       <c r="G28" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
+        <v>40</v>
       </c>
       <c r="H28" s="20" t="n">
         <f aca="false">IF(D28&lt;=0,0,CEILING(D28/G28,1))</f>
         <v>1</v>
       </c>
       <c r="I28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
-        <v>3</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
+        <v>1.95</v>
       </c>
       <c r="J28" s="24" t="n">
         <f aca="false">H28*I28</f>
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="K28" s="24" t="n">
-        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0))),CEILING(D28/INDEX(Prices!$K$5:$K$78,MATCH(C28,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0)),J28))</f>
-        <v>3</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>422</v>
-      </c>
+        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0))),CEILING(D28/INDEX(Prices!$K$5:$K$82,MATCH(C28,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0)),J28))</f>
+        <v>1.95</v>
+      </c>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
-        <v>0.07</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
+        <v>0.149</v>
       </c>
       <c r="F29" s="24" t="n">
         <f aca="false">D29*E29</f>
-        <v>0.49</v>
+        <v>4.917</v>
       </c>
       <c r="G29" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
-        <v>100</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
+        <v>10</v>
       </c>
       <c r="H29" s="20" t="n">
         <f aca="false">IF(D29&lt;=0,0,CEILING(D29/G29,1))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
-        <v>7</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
+        <v>1.49</v>
       </c>
       <c r="J29" s="24" t="n">
         <f aca="false">H29*I29</f>
-        <v>7</v>
+        <v>5.96</v>
       </c>
       <c r="K29" s="24" t="n">
-        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0))),CEILING(D29/INDEX(Prices!$K$5:$K$78,MATCH(C29,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0)),J29))</f>
-        <v>7</v>
+        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0))),CEILING(D29/INDEX(Prices!$K$5:$K$82,MATCH(C29,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0)),J29))</f>
+        <v>5.96</v>
       </c>
       <c r="L29" s="21" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>289</v>
+        <v>203</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
-        <v>0.99</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
+        <v>0.1475</v>
       </c>
       <c r="F30" s="24" t="n">
         <f aca="false">D30*E30</f>
-        <v>0.99</v>
+        <v>0.295</v>
       </c>
       <c r="G30" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
+        <v>20</v>
       </c>
       <c r="H30" s="20" t="n">
         <f aca="false">IF(D30&lt;=0,0,CEILING(D30/G30,1))</f>
         <v>1</v>
       </c>
       <c r="I30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
-        <v>0.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
+        <v>2.95</v>
       </c>
       <c r="J30" s="24" t="n">
         <f aca="false">H30*I30</f>
-        <v>0.99</v>
+        <v>2.95</v>
       </c>
       <c r="K30" s="24" t="n">
-        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0))),CEILING(D30/INDEX(Prices!$K$5:$K$78,MATCH(C30,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0)),J30))</f>
-        <v>0.99</v>
-      </c>
-      <c r="L30" s="21" t="s">
-        <v>427</v>
-      </c>
+        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0))),CEILING(D30/INDEX(Prices!$K$5:$K$82,MATCH(C30,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0)),J30))</f>
+        <v>2.95</v>
+      </c>
+      <c r="L30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>302</v>
+        <v>441</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
-        <v>0.25</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
+        <v>0.04</v>
       </c>
       <c r="F31" s="24" t="n">
         <f aca="false">D31*E31</f>
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="G31" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
-        <v>4</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
+        <v>100</v>
       </c>
       <c r="H31" s="20" t="n">
         <f aca="false">IF(D31&lt;=0,0,CEILING(D31/G31,1))</f>
         <v>1</v>
       </c>
       <c r="I31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
       </c>
       <c r="J31" s="24" t="n">
         <f aca="false">H31*I31</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="24" t="n">
-        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0))),CEILING(D31/INDEX(Prices!$K$5:$K$78,MATCH(C31,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0)),J31))</f>
-        <v>1</v>
+        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0))),CEILING(D31/INDEX(Prices!$K$5:$K$82,MATCH(C31,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0)),J31))</f>
+        <v>4</v>
       </c>
       <c r="L31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>88</v>
+        <v>376</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
-        <v>4.995</v>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
+        <v>0.16</v>
       </c>
       <c r="F32" s="24" t="n">
         <f aca="false">D32*E32</f>
-        <v>2.4975</v>
+        <v>0.64</v>
       </c>
       <c r="G32" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
-        <v>2</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
+        <v>25</v>
       </c>
       <c r="H32" s="20" t="n">
         <f aca="false">IF(D32&lt;=0,0,CEILING(D32/G32,1))</f>
         <v>1</v>
       </c>
       <c r="I32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
-        <v>9.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
       </c>
       <c r="J32" s="24" t="n">
         <f aca="false">H32*I32</f>
+        <v>4</v>
+      </c>
+      <c r="K32" s="24" t="n">
+        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0))),CEILING(D32/INDEX(Prices!$K$5:$K$82,MATCH(C32,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0)),J32))</f>
+        <v>4</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <f aca="false">D33*E33</f>
+        <v>3</v>
+      </c>
+      <c r="G33" s="28" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <f aca="false">IF(D33&lt;=0,0,CEILING(D33/G33,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
+        <v>3</v>
+      </c>
+      <c r="J33" s="24" t="n">
+        <f aca="false">H33*I33</f>
+        <v>3</v>
+      </c>
+      <c r="K33" s="24" t="n">
+        <f aca="false">IF(D33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0))),CEILING(D33/INDEX(Prices!$K$5:$K$82,MATCH(C33,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0)),J33))</f>
+        <v>3</v>
+      </c>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
+        <v>0.99</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <f aca="false">D34*E34</f>
+        <v>0.99</v>
+      </c>
+      <c r="G34" s="28" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <f aca="false">IF(D34&lt;=0,0,CEILING(D34/G34,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
+        <v>0.99</v>
+      </c>
+      <c r="J34" s="24" t="n">
+        <f aca="false">H34*I34</f>
+        <v>0.99</v>
+      </c>
+      <c r="K34" s="24" t="n">
+        <f aca="false">IF(D34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0))),CEILING(D34/INDEX(Prices!$K$5:$K$82,MATCH(C34,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0)),J34))</f>
+        <v>0.99</v>
+      </c>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
+        <v>0.25</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <f aca="false">D35*E35</f>
+        <v>1</v>
+      </c>
+      <c r="G35" s="28" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <f aca="false">IF(D35&lt;=0,0,CEILING(D35/G35,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="24" t="n">
+        <f aca="false">H35*I35</f>
+        <v>1</v>
+      </c>
+      <c r="K35" s="24" t="n">
+        <f aca="false">IF(D35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0))),CEILING(D35/INDEX(Prices!$K$5:$K$82,MATCH(C35,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0)),J35))</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
+        <v>4.995</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <f aca="false">D36*E36</f>
+        <v>2.4975</v>
+      </c>
+      <c r="G36" s="28" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <f aca="false">IF(D36&lt;=0,0,CEILING(D36/G36,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
-      <c r="K32" s="24" t="n">
-        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0))),CEILING(D32/INDEX(Prices!$K$5:$K$78,MATCH(C32,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0)),J32))</f>
+      <c r="J36" s="24" t="n">
+        <f aca="false">H36*I36</f>
         <v>9.99</v>
       </c>
-      <c r="L32" s="21"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D35" s="30" t="n">
+      <c r="K36" s="24" t="n">
+        <f aca="false">IF(D36&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C36,Prices!$A$5:$A$82,0))),CEILING(D36/INDEX(Prices!$K$5:$K$82,MATCH(C36,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C36,Prices!$A$5:$A$82,0)),J36))</f>
+        <v>9.99</v>
+      </c>
+      <c r="L36" s="21"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D39" s="30" t="n">
         <v>0.33</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E39" s="8" t="n">
         <f aca="false">Summary!$C$9</f>
         <v>14.99</v>
       </c>
-      <c r="F35" s="31" t="n">
-        <f aca="false">D35*E35</f>
+      <c r="F39" s="31" t="n">
+        <f aca="false">D39*E39</f>
         <v>4.9467</v>
       </c>
-      <c r="J35" s="31" t="n">
-        <f aca="false">CEILING(D35,1)*E35</f>
+      <c r="J39" s="31" t="n">
+        <f aca="false">CEILING(D39,1)*E39</f>
         <v>14.99</v>
       </c>
-      <c r="K35" s="31" t="n">
-        <f aca="false">F35</f>
+      <c r="K39" s="31" t="n">
+        <f aca="false">F39</f>
         <v>4.9467</v>
       </c>
-      <c r="L35" s="4" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D36" s="30" t="n">
+      <c r="L39" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D40" s="30" t="n">
         <v>30.2</v>
       </c>
-      <c r="E36" s="32" t="n">
+      <c r="E40" s="32" t="n">
         <f aca="false">Summary!$C$11*Summary!$C$10</f>
         <v>0.014256</v>
       </c>
-      <c r="F36" s="31" t="n">
-        <f aca="false">D36*E36</f>
+      <c r="F40" s="31" t="n">
+        <f aca="false">D40*E40</f>
         <v>0.4305312</v>
       </c>
-      <c r="J36" s="31" t="n">
-        <f aca="false">D36*E36</f>
+      <c r="J40" s="31" t="n">
+        <f aca="false">D40*E40</f>
         <v>0.4305312</v>
       </c>
-      <c r="K36" s="31" t="n">
-        <f aca="false">D36*E36</f>
+      <c r="K40" s="31" t="n">
+        <f aca="false">D40*E40</f>
         <v>0.4305312</v>
       </c>
-      <c r="L36" s="4" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="33" t="s">
+      <c r="L40" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="34" t="n">
-        <f aca="false">SUM(F5:F32)+F35+F36</f>
-        <v>153.2462312</v>
-      </c>
-      <c r="J38" s="34" t="n">
-        <f aca="false">SUM(J5:J32)+J35+J36</f>
-        <v>250.8105312</v>
-      </c>
-      <c r="K38" s="34" t="n">
-        <f aca="false">SUM(K5:K32)+K35+K36</f>
-        <v>229.3015322</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="F39" s="31" t="n">
-        <f aca="false">F38*Summary!$C$7</f>
-        <v>22.98693468</v>
-      </c>
-      <c r="J39" s="31" t="n">
-        <f aca="false">J38*Summary!$C$7</f>
-        <v>37.62157968</v>
-      </c>
-      <c r="K39" s="31" t="n">
-        <f aca="false">K38*Summary!$C$7</f>
-        <v>34.39522983</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="33" t="s">
+      <c r="F42" s="34" t="n">
+        <f aca="false">SUM(F5:F36)+F39+F40</f>
+        <v>157.4672312</v>
+      </c>
+      <c r="J42" s="34" t="n">
+        <f aca="false">SUM(J5:J36)+J39+J40</f>
+        <v>258.5805312</v>
+      </c>
+      <c r="K42" s="34" t="n">
+        <f aca="false">SUM(K5:K36)+K39+K40</f>
+        <v>237.0715322</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="F43" s="31" t="n">
+        <f aca="false">F42*Summary!$C$7</f>
+        <v>23.62008468</v>
+      </c>
+      <c r="J43" s="31" t="n">
+        <f aca="false">J42*Summary!$C$7</f>
+        <v>38.78707968</v>
+      </c>
+      <c r="K43" s="31" t="n">
+        <f aca="false">K42*Summary!$C$7</f>
+        <v>35.56072983</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="34" t="n">
-        <f aca="false">F38+F39</f>
-        <v>176.23316588</v>
-      </c>
-      <c r="J40" s="34" t="n">
-        <f aca="false">J38+J39</f>
-        <v>288.43211088</v>
-      </c>
-      <c r="K40" s="34" t="n">
-        <f aca="false">K38+K39</f>
-        <v>263.69676203</v>
+      <c r="F44" s="34" t="n">
+        <f aca="false">F42+F43</f>
+        <v>181.08731588</v>
+      </c>
+      <c r="J44" s="34" t="n">
+        <f aca="false">J42+J43</f>
+        <v>297.36761088</v>
+      </c>
+      <c r="K44" s="34" t="n">
+        <f aca="false">K42+K43</f>
+        <v>272.63226203</v>
       </c>
     </row>
   </sheetData>
@@ -7047,12 +7442,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7068,48 +7463,48 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>40</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>41</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>263</v>
@@ -7118,7 +7513,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>7.99</v>
       </c>
       <c r="F5" s="24" t="n">
@@ -7126,7 +7521,7 @@
         <v>15.98</v>
       </c>
       <c r="G5" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H5" s="20" t="n">
@@ -7134,7 +7529,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>7.99</v>
       </c>
       <c r="J5" s="24" t="n">
@@ -7142,17 +7537,17 @@
         <v>15.98</v>
       </c>
       <c r="K5" s="24" t="n">
-        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0))),CEILING(D5/INDEX(Prices!$K$5:$K$78,MATCH(C5,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0)),J5))</f>
+        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0))),CEILING(D5/INDEX(Prices!$K$5:$K$82,MATCH(C5,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0)),J5))</f>
         <v>15.98</v>
       </c>
       <c r="L5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>156</v>
@@ -7161,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>3.845</v>
       </c>
       <c r="F6" s="24" t="n">
@@ -7169,7 +7564,7 @@
         <v>3.845</v>
       </c>
       <c r="G6" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="H6" s="20" t="n">
@@ -7177,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>7.69</v>
       </c>
       <c r="J6" s="24" t="n">
@@ -7185,28 +7580,28 @@
         <v>7.69</v>
       </c>
       <c r="K6" s="24" t="n">
-        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0))),CEILING(D6/INDEX(Prices!$K$5:$K$78,MATCH(C6,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0)),J6))</f>
+        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0))),CEILING(D6/INDEX(Prices!$K$5:$K$82,MATCH(C6,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0)),J6))</f>
         <v>7.69</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D7" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>7.07</v>
       </c>
       <c r="F7" s="24" t="n">
@@ -7214,7 +7609,7 @@
         <v>7.07</v>
       </c>
       <c r="G7" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H7" s="20" t="n">
@@ -7222,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>7.07</v>
       </c>
       <c r="J7" s="24" t="n">
@@ -7230,17 +7625,17 @@
         <v>7.07</v>
       </c>
       <c r="K7" s="24" t="n">
-        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0))),CEILING(D7/INDEX(Prices!$K$5:$K$78,MATCH(C7,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0)),J7))</f>
+        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0))),CEILING(D7/INDEX(Prices!$K$5:$K$82,MATCH(C7,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0)),J7))</f>
         <v>7.07</v>
       </c>
       <c r="L7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>123</v>
@@ -7249,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="F8" s="24" t="n">
@@ -7257,7 +7652,7 @@
         <v>9.86</v>
       </c>
       <c r="G8" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H8" s="20" t="n">
@@ -7265,7 +7660,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="J8" s="24" t="n">
@@ -7273,17 +7668,17 @@
         <v>9.86</v>
       </c>
       <c r="K8" s="24" t="n">
-        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0))),CEILING(D8/INDEX(Prices!$K$5:$K$78,MATCH(C8,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0)),J8))</f>
+        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0))),CEILING(D8/INDEX(Prices!$K$5:$K$82,MATCH(C8,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0)),J8))</f>
         <v>9.86</v>
       </c>
       <c r="L8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>143</v>
@@ -7292,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>4.93</v>
       </c>
       <c r="F9" s="24" t="n">
@@ -7300,7 +7695,7 @@
         <v>4.93</v>
       </c>
       <c r="G9" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H9" s="20" t="n">
@@ -7308,7 +7703,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>4.93</v>
       </c>
       <c r="J9" s="24" t="n">
@@ -7316,17 +7711,17 @@
         <v>4.93</v>
       </c>
       <c r="K9" s="24" t="n">
-        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0))),CEILING(D9/INDEX(Prices!$K$5:$K$78,MATCH(C9,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0)),J9))</f>
+        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0))),CEILING(D9/INDEX(Prices!$K$5:$K$82,MATCH(C9,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0)),J9))</f>
         <v>4.93</v>
       </c>
       <c r="L9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>50</v>
@@ -7335,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>2.99</v>
       </c>
       <c r="F10" s="24" t="n">
@@ -7343,7 +7738,7 @@
         <v>2.99</v>
       </c>
       <c r="G10" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H10" s="20" t="n">
@@ -7351,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>2.99</v>
       </c>
       <c r="J10" s="24" t="n">
@@ -7359,17 +7754,17 @@
         <v>2.99</v>
       </c>
       <c r="K10" s="24" t="n">
-        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0))),CEILING(D10/INDEX(Prices!$K$5:$K$78,MATCH(C10,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0)),J10))</f>
+        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0))),CEILING(D10/INDEX(Prices!$K$5:$K$82,MATCH(C10,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0)),J10))</f>
         <v>2.99</v>
       </c>
       <c r="L10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>71</v>
@@ -7378,7 +7773,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>23</v>
       </c>
       <c r="F11" s="24" t="n">
@@ -7386,7 +7781,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H11" s="20" t="n">
@@ -7394,7 +7789,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>23</v>
       </c>
       <c r="J11" s="24" t="n">
@@ -7402,17 +7797,17 @@
         <v>46</v>
       </c>
       <c r="K11" s="24" t="n">
-        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0))),CEILING(D11/INDEX(Prices!$K$5:$K$78,MATCH(C11,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0)),J11))</f>
+        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0))),CEILING(D11/INDEX(Prices!$K$5:$K$82,MATCH(C11,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0)),J11))</f>
         <v>20.961514</v>
       </c>
       <c r="L11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>152</v>
@@ -7421,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="F12" s="24" t="n">
@@ -7429,7 +7824,7 @@
         <v>1.95</v>
       </c>
       <c r="G12" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H12" s="20" t="n">
@@ -7437,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="J12" s="24" t="n">
@@ -7445,17 +7840,17 @@
         <v>1.95</v>
       </c>
       <c r="K12" s="24" t="n">
-        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0))),CEILING(D12/INDEX(Prices!$K$5:$K$78,MATCH(C12,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0)),J12))</f>
+        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0))),CEILING(D12/INDEX(Prices!$K$5:$K$82,MATCH(C12,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0)),J12))</f>
         <v>1.95</v>
       </c>
       <c r="L12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>82</v>
@@ -7464,7 +7859,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>20.28985</v>
       </c>
       <c r="F13" s="24" t="n">
@@ -7472,7 +7867,7 @@
         <v>20.28985</v>
       </c>
       <c r="G13" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H13" s="20" t="n">
@@ -7480,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>20.28985</v>
       </c>
       <c r="J13" s="24" t="n">
@@ -7488,17 +7883,17 @@
         <v>20.28985</v>
       </c>
       <c r="K13" s="24" t="n">
-        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0))),CEILING(D13/INDEX(Prices!$K$5:$K$78,MATCH(C13,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0)),J13))</f>
+        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0))),CEILING(D13/INDEX(Prices!$K$5:$K$82,MATCH(C13,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0)),J13))</f>
         <v>20.28985</v>
       </c>
       <c r="L13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>258</v>
@@ -7507,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>1.665167</v>
       </c>
       <c r="F14" s="24" t="n">
@@ -7515,7 +7910,7 @@
         <v>1.665167</v>
       </c>
       <c r="G14" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H14" s="20" t="n">
@@ -7523,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>8.325835</v>
       </c>
       <c r="J14" s="24" t="n">
@@ -7531,26 +7926,26 @@
         <v>8.325835</v>
       </c>
       <c r="K14" s="24" t="n">
-        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0))),CEILING(D14/INDEX(Prices!$K$5:$K$78,MATCH(C14,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0)),J14))</f>
+        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0))),CEILING(D14/INDEX(Prices!$K$5:$K$82,MATCH(C14,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0)),J14))</f>
         <v>8.325835</v>
       </c>
       <c r="L14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D15" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>2.29</v>
       </c>
       <c r="F15" s="24" t="n">
@@ -7558,7 +7953,7 @@
         <v>2.29</v>
       </c>
       <c r="G15" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H15" s="20" t="n">
@@ -7566,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>2.29</v>
       </c>
       <c r="J15" s="24" t="n">
@@ -7574,17 +7969,17 @@
         <v>2.29</v>
       </c>
       <c r="K15" s="24" t="n">
-        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0))),CEILING(D15/INDEX(Prices!$K$5:$K$78,MATCH(C15,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0)),J15))</f>
+        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0))),CEILING(D15/INDEX(Prices!$K$5:$K$82,MATCH(C15,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0)),J15))</f>
         <v>2.29</v>
       </c>
       <c r="L15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>67</v>
@@ -7593,7 +7988,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="F16" s="24" t="n">
@@ -7601,7 +7996,7 @@
         <v>0.71</v>
       </c>
       <c r="G16" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H16" s="20" t="n">
@@ -7609,7 +8004,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="J16" s="24" t="n">
@@ -7617,17 +8012,17 @@
         <v>0.71</v>
       </c>
       <c r="K16" s="24" t="n">
-        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0))),CEILING(D16/INDEX(Prices!$K$5:$K$78,MATCH(C16,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0)),J16))</f>
+        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0))),CEILING(D16/INDEX(Prices!$K$5:$K$82,MATCH(C16,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0)),J16))</f>
         <v>0.71</v>
       </c>
       <c r="L16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>78</v>
@@ -7636,7 +8031,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>0.398</v>
       </c>
       <c r="F17" s="24" t="n">
@@ -7644,7 +8039,7 @@
         <v>1.194</v>
       </c>
       <c r="G17" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H17" s="20" t="n">
@@ -7652,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>1.99</v>
       </c>
       <c r="J17" s="24" t="n">
@@ -7660,17 +8055,17 @@
         <v>1.99</v>
       </c>
       <c r="K17" s="24" t="n">
-        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0))),CEILING(D17/INDEX(Prices!$K$5:$K$78,MATCH(C17,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0)),J17))</f>
+        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0))),CEILING(D17/INDEX(Prices!$K$5:$K$82,MATCH(C17,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0)),J17))</f>
         <v>1.99</v>
       </c>
       <c r="L17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>305</v>
@@ -7679,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>0.398</v>
       </c>
       <c r="F18" s="24" t="n">
@@ -7687,7 +8082,7 @@
         <v>0.398</v>
       </c>
       <c r="G18" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H18" s="20" t="n">
@@ -7695,7 +8090,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>1.99</v>
       </c>
       <c r="J18" s="24" t="n">
@@ -7703,17 +8098,17 @@
         <v>1.99</v>
       </c>
       <c r="K18" s="24" t="n">
-        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0))),CEILING(D18/INDEX(Prices!$K$5:$K$78,MATCH(C18,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0)),J18))</f>
+        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0))),CEILING(D18/INDEX(Prices!$K$5:$K$82,MATCH(C18,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0)),J18))</f>
         <v>1.99</v>
       </c>
       <c r="L18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>297</v>
@@ -7722,7 +8117,7 @@
         <v>0.1</v>
       </c>
       <c r="E19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>12.95</v>
       </c>
       <c r="F19" s="24" t="n">
@@ -7730,7 +8125,7 @@
         <v>1.295</v>
       </c>
       <c r="G19" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H19" s="20" t="n">
@@ -7738,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>12.95</v>
       </c>
       <c r="J19" s="24" t="n">
@@ -7746,19 +8141,19 @@
         <v>12.95</v>
       </c>
       <c r="K19" s="24" t="n">
-        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0))),CEILING(D19/INDEX(Prices!$K$5:$K$78,MATCH(C19,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0)),J19))</f>
+        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0))),CEILING(D19/INDEX(Prices!$K$5:$K$82,MATCH(C19,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0)),J19))</f>
         <v>12.95</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="C20" s="28" t="s">
         <v>293</v>
@@ -7767,7 +8162,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>0.1</v>
       </c>
       <c r="F20" s="24" t="n">
@@ -7775,7 +8170,7 @@
         <v>0.1</v>
       </c>
       <c r="G20" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H20" s="20" t="n">
@@ -7783,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="J20" s="24" t="n">
@@ -7791,19 +8186,19 @@
         <v>1</v>
       </c>
       <c r="K20" s="24" t="n">
-        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0))),CEILING(D20/INDEX(Prices!$K$5:$K$78,MATCH(C20,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0)),J20))</f>
+        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0))),CEILING(D20/INDEX(Prices!$K$5:$K$82,MATCH(C20,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0)),J20))</f>
         <v>1</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C21" s="28" t="s">
         <v>169</v>
@@ -7812,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>0.1425</v>
       </c>
       <c r="F21" s="24" t="n">
@@ -7820,7 +8215,7 @@
         <v>2.1375</v>
       </c>
       <c r="G21" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="H21" s="20" t="n">
@@ -7828,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>5.7</v>
       </c>
       <c r="J21" s="24" t="n">
@@ -7836,26 +8231,26 @@
         <v>5.7</v>
       </c>
       <c r="K21" s="24" t="n">
-        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0))),CEILING(D21/INDEX(Prices!$K$5:$K$78,MATCH(C21,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0)),J21))</f>
+        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0))),CEILING(D21/INDEX(Prices!$K$5:$K$82,MATCH(C21,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0)),J21))</f>
         <v>5.7</v>
       </c>
       <c r="L21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D22" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="E22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>19.93</v>
       </c>
       <c r="F22" s="24" t="n">
@@ -7863,7 +8258,7 @@
         <v>1.993</v>
       </c>
       <c r="G22" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H22" s="20" t="n">
@@ -7871,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>19.93</v>
       </c>
       <c r="J22" s="24" t="n">
@@ -7879,19 +8274,19 @@
         <v>19.93</v>
       </c>
       <c r="K22" s="24" t="n">
-        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0))),CEILING(D22/INDEX(Prices!$K$5:$K$78,MATCH(C22,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0)),J22))</f>
+        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0))),CEILING(D22/INDEX(Prices!$K$5:$K$82,MATCH(C22,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0)),J22))</f>
         <v>19.93</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C23" s="28" t="s">
         <v>148</v>
@@ -7900,7 +8295,7 @@
         <v>0.1</v>
       </c>
       <c r="E23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>12.84</v>
       </c>
       <c r="F23" s="24" t="n">
@@ -7908,7 +8303,7 @@
         <v>1.284</v>
       </c>
       <c r="G23" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H23" s="20" t="n">
@@ -7916,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>12.84</v>
       </c>
       <c r="J23" s="24" t="n">
@@ -7924,28 +8319,28 @@
         <v>12.84</v>
       </c>
       <c r="K23" s="24" t="n">
-        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0))),CEILING(D23/INDEX(Prices!$K$5:$K$78,MATCH(C23,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0)),J23))</f>
+        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0))),CEILING(D23/INDEX(Prices!$K$5:$K$82,MATCH(C23,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0)),J23))</f>
         <v>12.84</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>0.0599</v>
       </c>
       <c r="F24" s="24" t="n">
@@ -7953,7 +8348,7 @@
         <v>0.2995</v>
       </c>
       <c r="G24" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="H24" s="20" t="n">
@@ -7961,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>5.99</v>
       </c>
       <c r="J24" s="24" t="n">
@@ -7969,26 +8364,26 @@
         <v>5.99</v>
       </c>
       <c r="K24" s="24" t="n">
-        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0))),CEILING(D24/INDEX(Prices!$K$5:$K$78,MATCH(C24,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0)),J24))</f>
+        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0))),CEILING(D24/INDEX(Prices!$K$5:$K$82,MATCH(C24,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0)),J24))</f>
         <v>5.99</v>
       </c>
       <c r="L24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D25" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>4.491753</v>
       </c>
       <c r="F25" s="24" t="n">
@@ -7996,7 +8391,7 @@
         <v>4.491753</v>
       </c>
       <c r="G25" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="H25" s="20" t="n">
@@ -8004,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>8.983506</v>
       </c>
       <c r="J25" s="24" t="n">
@@ -8012,17 +8407,17 @@
         <v>8.983506</v>
       </c>
       <c r="K25" s="24" t="n">
-        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0))),CEILING(D25/INDEX(Prices!$K$5:$K$78,MATCH(C25,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0)),J25))</f>
+        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0))),CEILING(D25/INDEX(Prices!$K$5:$K$82,MATCH(C25,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0)),J25))</f>
         <v>8.983506</v>
       </c>
       <c r="L25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="C26" s="28" t="s">
         <v>221</v>
@@ -8031,7 +8426,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>1.2</v>
       </c>
       <c r="F26" s="24" t="n">
@@ -8039,7 +8434,7 @@
         <v>4.8</v>
       </c>
       <c r="G26" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H26" s="20" t="n">
@@ -8047,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="J26" s="24" t="n">
@@ -8055,19 +8450,19 @@
         <v>12</v>
       </c>
       <c r="K26" s="24" t="n">
-        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0))),CEILING(D26/INDEX(Prices!$K$5:$K$78,MATCH(C26,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0)),J26))</f>
+        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0))),CEILING(D26/INDEX(Prices!$K$5:$K$82,MATCH(C26,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0)),J26))</f>
         <v>12</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="C27" s="28" t="s">
         <v>216</v>
@@ -8076,7 +8471,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>1.1</v>
       </c>
       <c r="F27" s="24" t="n">
@@ -8084,7 +8479,7 @@
         <v>2.2</v>
       </c>
       <c r="G27" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H27" s="20" t="n">
@@ -8092,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>11</v>
       </c>
       <c r="J27" s="24" t="n">
@@ -8100,17 +8495,17 @@
         <v>11</v>
       </c>
       <c r="K27" s="24" t="n">
-        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0))),CEILING(D27/INDEX(Prices!$K$5:$K$78,MATCH(C27,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0)),J27))</f>
+        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0))),CEILING(D27/INDEX(Prices!$K$5:$K$82,MATCH(C27,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0)),J27))</f>
         <v>11</v>
       </c>
       <c r="L27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>236</v>
@@ -8119,7 +8514,7 @@
         <v>0.08</v>
       </c>
       <c r="E28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>24</v>
       </c>
       <c r="F28" s="24" t="n">
@@ -8127,7 +8522,7 @@
         <v>1.92</v>
       </c>
       <c r="G28" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H28" s="20" t="n">
@@ -8135,7 +8530,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>24</v>
       </c>
       <c r="J28" s="24" t="n">
@@ -8143,19 +8538,19 @@
         <v>24</v>
       </c>
       <c r="K28" s="24" t="n">
-        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0))),CEILING(D28/INDEX(Prices!$K$5:$K$78,MATCH(C28,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0)),J28))</f>
+        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0))),CEILING(D28/INDEX(Prices!$K$5:$K$82,MATCH(C28,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0)),J28))</f>
         <v>24</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>232</v>
@@ -8164,7 +8559,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="F29" s="24" t="n">
@@ -8172,7 +8567,7 @@
         <v>0.3</v>
       </c>
       <c r="G29" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H29" s="20" t="n">
@@ -8180,7 +8575,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="J29" s="24" t="n">
@@ -8188,14 +8583,14 @@
         <v>0.3</v>
       </c>
       <c r="K29" s="24" t="n">
-        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0))),CEILING(D29/INDEX(Prices!$K$5:$K$78,MATCH(C29,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0)),J29))</f>
+        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0))),CEILING(D29/INDEX(Prices!$K$5:$K$82,MATCH(C29,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0)),J29))</f>
         <v>0.3</v>
       </c>
       <c r="L29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B30" s="21" t="s">
         <v>229</v>
@@ -8207,7 +8602,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>0.095</v>
       </c>
       <c r="F30" s="24" t="n">
@@ -8215,7 +8610,7 @@
         <v>0.57</v>
       </c>
       <c r="G30" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H30" s="20" t="n">
@@ -8223,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>0.95</v>
       </c>
       <c r="J30" s="24" t="n">
@@ -8231,17 +8626,17 @@
         <v>0.95</v>
       </c>
       <c r="K30" s="24" t="n">
-        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0))),CEILING(D30/INDEX(Prices!$K$5:$K$78,MATCH(C30,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0)),J30))</f>
+        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0))),CEILING(D30/INDEX(Prices!$K$5:$K$82,MATCH(C30,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0)),J30))</f>
         <v>0.95</v>
       </c>
       <c r="L30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>225</v>
@@ -8250,7 +8645,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>0.06</v>
       </c>
       <c r="F31" s="24" t="n">
@@ -8258,7 +8653,7 @@
         <v>0.36</v>
       </c>
       <c r="G31" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>50</v>
       </c>
       <c r="H31" s="20" t="n">
@@ -8266,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>3</v>
       </c>
       <c r="J31" s="24" t="n">
@@ -8274,14 +8669,14 @@
         <v>3</v>
       </c>
       <c r="K31" s="24" t="n">
-        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0))),CEILING(D31/INDEX(Prices!$K$5:$K$78,MATCH(C31,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0)),J31))</f>
+        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0))),CEILING(D31/INDEX(Prices!$K$5:$K$82,MATCH(C31,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0)),J31))</f>
         <v>3</v>
       </c>
       <c r="L31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B32" s="21" t="s">
         <v>244</v>
@@ -8293,7 +8688,7 @@
         <v>26</v>
       </c>
       <c r="E32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>0.04875</v>
       </c>
       <c r="F32" s="24" t="n">
@@ -8301,7 +8696,7 @@
         <v>1.2675</v>
       </c>
       <c r="G32" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="H32" s="20" t="n">
@@ -8309,7 +8704,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="J32" s="24" t="n">
@@ -8317,14 +8712,14 @@
         <v>1.95</v>
       </c>
       <c r="K32" s="24" t="n">
-        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0))),CEILING(D32/INDEX(Prices!$K$5:$K$78,MATCH(C32,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0)),J32))</f>
+        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0))),CEILING(D32/INDEX(Prices!$K$5:$K$82,MATCH(C32,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0)),J32))</f>
         <v>1.95</v>
       </c>
       <c r="L32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B33" s="21" t="s">
         <v>241</v>
@@ -8336,7 +8731,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>0.1</v>
       </c>
       <c r="F33" s="24" t="n">
@@ -8344,7 +8739,7 @@
         <v>0.2</v>
       </c>
       <c r="G33" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>50</v>
       </c>
       <c r="H33" s="20" t="n">
@@ -8352,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="J33" s="24" t="n">
@@ -8360,14 +8755,14 @@
         <v>5</v>
       </c>
       <c r="K33" s="24" t="n">
-        <f aca="false">IF(D33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C33,Prices!$A$5:$A$78,0))),CEILING(D33/INDEX(Prices!$K$5:$K$78,MATCH(C33,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C33,Prices!$A$5:$A$78,0)),J33))</f>
+        <f aca="false">IF(D33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0))),CEILING(D33/INDEX(Prices!$K$5:$K$82,MATCH(C33,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0)),J33))</f>
         <v>5</v>
       </c>
       <c r="L33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>161</v>
@@ -8379,7 +8774,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="F34" s="24" t="n">
@@ -8387,7 +8782,7 @@
         <v>0.6</v>
       </c>
       <c r="G34" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H34" s="20" t="n">
@@ -8395,7 +8790,7 @@
         <v>4</v>
       </c>
       <c r="I34" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="J34" s="24" t="n">
@@ -8403,17 +8798,17 @@
         <v>0.6</v>
       </c>
       <c r="K34" s="24" t="n">
-        <f aca="false">IF(D34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C34,Prices!$A$5:$A$78,0))),CEILING(D34/INDEX(Prices!$K$5:$K$78,MATCH(C34,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C34,Prices!$A$5:$A$78,0)),J34))</f>
+        <f aca="false">IF(D34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0))),CEILING(D34/INDEX(Prices!$K$5:$K$82,MATCH(C34,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0)),J34))</f>
         <v>0.6</v>
       </c>
       <c r="L34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="C35" s="28" t="s">
         <v>114</v>
@@ -8422,7 +8817,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>0.95</v>
       </c>
       <c r="F35" s="24" t="n">
@@ -8430,7 +8825,7 @@
         <v>17.1</v>
       </c>
       <c r="G35" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H35" s="20" t="n">
@@ -8438,7 +8833,7 @@
         <v>18</v>
       </c>
       <c r="I35" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>0.95</v>
       </c>
       <c r="J35" s="24" t="n">
@@ -8446,19 +8841,19 @@
         <v>17.1</v>
       </c>
       <c r="K35" s="24" t="n">
-        <f aca="false">IF(D35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C35,Prices!$A$5:$A$78,0))),CEILING(D35/INDEX(Prices!$K$5:$K$78,MATCH(C35,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C35,Prices!$A$5:$A$78,0)),J35))</f>
+        <f aca="false">IF(D35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0))),CEILING(D35/INDEX(Prices!$K$5:$K$82,MATCH(C35,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0)),J35))</f>
         <v>17.1</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="C36" s="28" t="s">
         <v>128</v>
@@ -8467,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C36,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="F36" s="24" t="n">
@@ -8475,7 +8870,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C36,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H36" s="20" t="n">
@@ -8483,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C36,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C36,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="J36" s="24" t="n">
@@ -8491,19 +8886,19 @@
         <v>12</v>
       </c>
       <c r="K36" s="24" t="n">
-        <f aca="false">IF(D36&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C36,Prices!$A$5:$A$78,0))),CEILING(D36/INDEX(Prices!$K$5:$K$78,MATCH(C36,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C36,Prices!$A$5:$A$78,0)),J36))</f>
+        <f aca="false">IF(D36&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C36,Prices!$A$5:$A$82,0))),CEILING(D36/INDEX(Prices!$K$5:$K$82,MATCH(C36,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C36,Prices!$A$5:$A$82,0)),J36))</f>
         <v>12</v>
       </c>
       <c r="L36" s="21" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="C37" s="28" t="s">
         <v>93</v>
@@ -8512,7 +8907,7 @@
         <v>0.2</v>
       </c>
       <c r="E37" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C37,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C37,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="F37" s="24" t="n">
@@ -8520,7 +8915,7 @@
         <v>1.998</v>
       </c>
       <c r="G37" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C37,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C37,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H37" s="20" t="n">
@@ -8528,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C37,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C37,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="J37" s="24" t="n">
@@ -8536,16 +8931,16 @@
         <v>9.99</v>
       </c>
       <c r="K37" s="24" t="n">
-        <f aca="false">IF(D37&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C37,Prices!$A$5:$A$78,0))),CEILING(D37/INDEX(Prices!$K$5:$K$78,MATCH(C37,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C37,Prices!$A$5:$A$78,0)),J37))</f>
+        <f aca="false">IF(D37&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C37,Prices!$A$5:$A$82,0))),CEILING(D37/INDEX(Prices!$K$5:$K$82,MATCH(C37,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C37,Prices!$A$5:$A$82,0)),J37))</f>
         <v>9.99</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>98</v>
@@ -8557,7 +8952,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C38,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C38,Prices!$A$5:$A$82,0))</f>
         <v>0.5825</v>
       </c>
       <c r="F38" s="24" t="n">
@@ -8565,7 +8960,7 @@
         <v>1.165</v>
       </c>
       <c r="G38" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C38,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C38,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="H38" s="20" t="n">
@@ -8573,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C38,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C38,Prices!$A$5:$A$82,0))</f>
         <v>6.99</v>
       </c>
       <c r="J38" s="24" t="n">
@@ -8581,17 +8976,17 @@
         <v>6.99</v>
       </c>
       <c r="K38" s="24" t="n">
-        <f aca="false">IF(D38&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C38,Prices!$A$5:$A$78,0))),CEILING(D38/INDEX(Prices!$K$5:$K$78,MATCH(C38,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C38,Prices!$A$5:$A$78,0)),J38))</f>
+        <f aca="false">IF(D38&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C38,Prices!$A$5:$A$82,0))),CEILING(D38/INDEX(Prices!$K$5:$K$82,MATCH(C38,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C38,Prices!$A$5:$A$82,0)),J38))</f>
         <v>6.99</v>
       </c>
       <c r="L38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="C39" s="28" t="s">
         <v>101</v>
@@ -8600,7 +8995,7 @@
         <v>0.2</v>
       </c>
       <c r="E39" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C39,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C39,Prices!$A$5:$A$82,0))</f>
         <v>11.41</v>
       </c>
       <c r="F39" s="24" t="n">
@@ -8608,7 +9003,7 @@
         <v>2.282</v>
       </c>
       <c r="G39" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C39,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C39,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H39" s="20" t="n">
@@ -8616,7 +9011,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C39,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C39,Prices!$A$5:$A$82,0))</f>
         <v>11.41</v>
       </c>
       <c r="J39" s="24" t="n">
@@ -8624,24 +9019,24 @@
         <v>11.41</v>
       </c>
       <c r="K39" s="24" t="n">
-        <f aca="false">IF(D39&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C39,Prices!$A$5:$A$78,0))),CEILING(D39/INDEX(Prices!$K$5:$K$78,MATCH(C39,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C39,Prices!$A$5:$A$78,0)),J39))</f>
+        <f aca="false">IF(D39&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C39,Prices!$A$5:$A$82,0))),CEILING(D39/INDEX(Prices!$K$5:$K$82,MATCH(C39,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C39,Prices!$A$5:$A$82,0)),J39))</f>
         <v>11.41</v>
       </c>
       <c r="L39" s="21" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="D42" s="30" t="n">
         <v>0.303</v>
@@ -8663,15 +9058,15 @@
         <v>4.54197</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D43" s="30" t="n">
         <v>30.4</v>
@@ -8693,7 +9088,7 @@
         <v>0.4333824</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8715,7 +9110,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="F46" s="31" t="n">
         <f aca="false">F45*Summary!$C$7</f>
@@ -8783,12 +9178,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8804,48 +9199,48 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>40</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>41</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>247</v>
@@ -8854,7 +9249,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>6</v>
       </c>
       <c r="F5" s="24" t="n">
@@ -8862,7 +9257,7 @@
         <v>108</v>
       </c>
       <c r="G5" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H5" s="20" t="n">
@@ -8870,7 +9265,7 @@
         <v>18</v>
       </c>
       <c r="I5" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C5,Prices!$A$5:$A$82,0))</f>
         <v>6</v>
       </c>
       <c r="J5" s="24" t="n">
@@ -8878,17 +9273,17 @@
         <v>108</v>
       </c>
       <c r="K5" s="24" t="n">
-        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0))),CEILING(D5/INDEX(Prices!$K$5:$K$78,MATCH(C5,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C5,Prices!$A$5:$A$78,0)),J5))</f>
+        <f aca="false">IF(D5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0))),CEILING(D5/INDEX(Prices!$K$5:$K$82,MATCH(C5,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C5,Prices!$A$5:$A$82,0)),J5))</f>
         <v>57.93102</v>
       </c>
       <c r="L5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>267</v>
@@ -8897,7 +9292,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>6.95</v>
       </c>
       <c r="F6" s="24" t="n">
@@ -8905,7 +9300,7 @@
         <v>13.9</v>
       </c>
       <c r="G6" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H6" s="20" t="n">
@@ -8913,7 +9308,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C6,Prices!$A$5:$A$82,0))</f>
         <v>6.95</v>
       </c>
       <c r="J6" s="24" t="n">
@@ -8921,17 +9316,17 @@
         <v>13.9</v>
       </c>
       <c r="K6" s="24" t="n">
-        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0))),CEILING(D6/INDEX(Prices!$K$5:$K$78,MATCH(C6,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C6,Prices!$A$5:$A$78,0)),J6))</f>
+        <f aca="false">IF(D6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0))),CEILING(D6/INDEX(Prices!$K$5:$K$82,MATCH(C6,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C6,Prices!$A$5:$A$82,0)),J6))</f>
         <v>13.9</v>
       </c>
       <c r="L6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>123</v>
@@ -8940,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="F7" s="24" t="n">
@@ -8948,7 +9343,7 @@
         <v>9.86</v>
       </c>
       <c r="G7" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H7" s="20" t="n">
@@ -8956,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C7,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="J7" s="24" t="n">
@@ -8964,17 +9359,17 @@
         <v>9.86</v>
       </c>
       <c r="K7" s="24" t="n">
-        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0))),CEILING(D7/INDEX(Prices!$K$5:$K$78,MATCH(C7,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C7,Prices!$A$5:$A$78,0)),J7))</f>
+        <f aca="false">IF(D7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0))),CEILING(D7/INDEX(Prices!$K$5:$K$82,MATCH(C7,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C7,Prices!$A$5:$A$82,0)),J7))</f>
         <v>9.86</v>
       </c>
       <c r="L7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>177</v>
@@ -8983,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>15.966013</v>
       </c>
       <c r="F8" s="24" t="n">
@@ -8991,7 +9386,7 @@
         <v>15.966013</v>
       </c>
       <c r="G8" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H8" s="20" t="n">
@@ -8999,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C8,Prices!$A$5:$A$82,0))</f>
         <v>15.966013</v>
       </c>
       <c r="J8" s="24" t="n">
@@ -9007,26 +9402,26 @@
         <v>15.966013</v>
       </c>
       <c r="K8" s="24" t="n">
-        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0))),CEILING(D8/INDEX(Prices!$K$5:$K$78,MATCH(C8,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C8,Prices!$A$5:$A$78,0)),J8))</f>
+        <f aca="false">IF(D8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0))),CEILING(D8/INDEX(Prices!$K$5:$K$82,MATCH(C8,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C8,Prices!$A$5:$A$82,0)),J8))</f>
         <v>15.966013</v>
       </c>
       <c r="L8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>34.968507</v>
       </c>
       <c r="F9" s="24" t="n">
@@ -9034,7 +9429,7 @@
         <v>34.968507</v>
       </c>
       <c r="G9" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H9" s="20" t="n">
@@ -9042,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C9,Prices!$A$5:$A$82,0))</f>
         <v>34.968507</v>
       </c>
       <c r="J9" s="24" t="n">
@@ -9050,17 +9445,17 @@
         <v>34.968507</v>
       </c>
       <c r="K9" s="24" t="n">
-        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0))),CEILING(D9/INDEX(Prices!$K$5:$K$78,MATCH(C9,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C9,Prices!$A$5:$A$78,0)),J9))</f>
+        <f aca="false">IF(D9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0))),CEILING(D9/INDEX(Prices!$K$5:$K$82,MATCH(C9,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C9,Prices!$A$5:$A$82,0)),J9))</f>
         <v>34.968507</v>
       </c>
       <c r="L9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>258</v>
@@ -9069,7 +9464,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>1.665167</v>
       </c>
       <c r="F10" s="24" t="n">
@@ -9077,7 +9472,7 @@
         <v>1.665167</v>
       </c>
       <c r="G10" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H10" s="20" t="n">
@@ -9085,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C10,Prices!$A$5:$A$82,0))</f>
         <v>8.325835</v>
       </c>
       <c r="J10" s="24" t="n">
@@ -9093,26 +9488,26 @@
         <v>8.325835</v>
       </c>
       <c r="K10" s="24" t="n">
-        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0))),CEILING(D10/INDEX(Prices!$K$5:$K$78,MATCH(C10,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C10,Prices!$A$5:$A$78,0)),J10))</f>
+        <f aca="false">IF(D10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0))),CEILING(D10/INDEX(Prices!$K$5:$K$82,MATCH(C10,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C10,Prices!$A$5:$A$82,0)),J10))</f>
         <v>8.325835</v>
       </c>
       <c r="L10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>3.99</v>
       </c>
       <c r="F11" s="24" t="n">
@@ -9120,7 +9515,7 @@
         <v>3.99</v>
       </c>
       <c r="G11" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H11" s="20" t="n">
@@ -9128,7 +9523,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C11,Prices!$A$5:$A$82,0))</f>
         <v>3.99</v>
       </c>
       <c r="J11" s="24" t="n">
@@ -9136,17 +9531,17 @@
         <v>3.99</v>
       </c>
       <c r="K11" s="24" t="n">
-        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0))),CEILING(D11/INDEX(Prices!$K$5:$K$78,MATCH(C11,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C11,Prices!$A$5:$A$78,0)),J11))</f>
+        <f aca="false">IF(D11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0))),CEILING(D11/INDEX(Prices!$K$5:$K$82,MATCH(C11,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C11,Prices!$A$5:$A$82,0)),J11))</f>
         <v>3.99</v>
       </c>
       <c r="L11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>134</v>
@@ -9155,7 +9550,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>6.945</v>
       </c>
       <c r="F12" s="24" t="n">
@@ -9163,7 +9558,7 @@
         <v>6.945</v>
       </c>
       <c r="G12" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="H12" s="20" t="n">
@@ -9171,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C12,Prices!$A$5:$A$82,0))</f>
         <v>13.89</v>
       </c>
       <c r="J12" s="24" t="n">
@@ -9179,26 +9574,26 @@
         <v>13.89</v>
       </c>
       <c r="K12" s="24" t="n">
-        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0))),CEILING(D12/INDEX(Prices!$K$5:$K$78,MATCH(C12,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C12,Prices!$A$5:$A$78,0)),J12))</f>
+        <f aca="false">IF(D12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0))),CEILING(D12/INDEX(Prices!$K$5:$K$82,MATCH(C12,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C12,Prices!$A$5:$A$82,0)),J12))</f>
         <v>13.89</v>
       </c>
       <c r="L12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>2.770614</v>
       </c>
       <c r="F13" s="24" t="n">
@@ -9206,7 +9601,7 @@
         <v>2.770614</v>
       </c>
       <c r="G13" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H13" s="20" t="n">
@@ -9214,7 +9609,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C13,Prices!$A$5:$A$82,0))</f>
         <v>2.770614</v>
       </c>
       <c r="J13" s="24" t="n">
@@ -9222,19 +9617,19 @@
         <v>2.770614</v>
       </c>
       <c r="K13" s="24" t="n">
-        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0))),CEILING(D13/INDEX(Prices!$K$5:$K$78,MATCH(C13,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C13,Prices!$A$5:$A$78,0)),J13))</f>
+        <f aca="false">IF(D13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0))),CEILING(D13/INDEX(Prices!$K$5:$K$82,MATCH(C13,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C13,Prices!$A$5:$A$82,0)),J13))</f>
         <v>2.770614</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>182</v>
@@ -9243,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>5.387305</v>
       </c>
       <c r="F14" s="24" t="n">
@@ -9251,7 +9646,7 @@
         <v>5.387305</v>
       </c>
       <c r="G14" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H14" s="20" t="n">
@@ -9259,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C14,Prices!$A$5:$A$82,0))</f>
         <v>5.387305</v>
       </c>
       <c r="J14" s="24" t="n">
@@ -9267,14 +9662,14 @@
         <v>5.387305</v>
       </c>
       <c r="K14" s="24" t="n">
-        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0))),CEILING(D14/INDEX(Prices!$K$5:$K$78,MATCH(C14,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C14,Prices!$A$5:$A$78,0)),J14))</f>
+        <f aca="false">IF(D14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0))),CEILING(D14/INDEX(Prices!$K$5:$K$82,MATCH(C14,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C14,Prices!$A$5:$A$82,0)),J14))</f>
         <v>5.387305</v>
       </c>
       <c r="L14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B15" s="21" t="s">
         <v>191</v>
@@ -9286,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>28.57</v>
       </c>
       <c r="F15" s="24" t="n">
@@ -9294,7 +9689,7 @@
         <v>28.57</v>
       </c>
       <c r="G15" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H15" s="20" t="n">
@@ -9302,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C15,Prices!$A$5:$A$82,0))</f>
         <v>28.57</v>
       </c>
       <c r="J15" s="24" t="n">
@@ -9310,17 +9705,17 @@
         <v>28.57</v>
       </c>
       <c r="K15" s="24" t="n">
-        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0))),CEILING(D15/INDEX(Prices!$K$5:$K$78,MATCH(C15,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C15,Prices!$A$5:$A$78,0)),J15))</f>
+        <f aca="false">IF(D15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0))),CEILING(D15/INDEX(Prices!$K$5:$K$82,MATCH(C15,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C15,Prices!$A$5:$A$82,0)),J15))</f>
         <v>28.57</v>
       </c>
       <c r="L15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>186</v>
@@ -9329,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>14.97251</v>
       </c>
       <c r="F16" s="24" t="n">
@@ -9337,7 +9732,7 @@
         <v>14.97251</v>
       </c>
       <c r="G16" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H16" s="20" t="n">
@@ -9345,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C16,Prices!$A$5:$A$82,0))</f>
         <v>14.97251</v>
       </c>
       <c r="J16" s="24" t="n">
@@ -9353,17 +9748,17 @@
         <v>14.97251</v>
       </c>
       <c r="K16" s="24" t="n">
-        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0))),CEILING(D16/INDEX(Prices!$K$5:$K$78,MATCH(C16,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C16,Prices!$A$5:$A$78,0)),J16))</f>
+        <f aca="false">IF(D16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0))),CEILING(D16/INDEX(Prices!$K$5:$K$82,MATCH(C16,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C16,Prices!$A$5:$A$82,0)),J16))</f>
         <v>14.97251</v>
       </c>
       <c r="L16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>62</v>
@@ -9372,7 +9767,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="F17" s="24" t="n">
@@ -9380,7 +9775,7 @@
         <v>1.42</v>
       </c>
       <c r="G17" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H17" s="20" t="n">
@@ -9388,7 +9783,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C17,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="J17" s="24" t="n">
@@ -9396,17 +9791,17 @@
         <v>1.42</v>
       </c>
       <c r="K17" s="24" t="n">
-        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0))),CEILING(D17/INDEX(Prices!$K$5:$K$78,MATCH(C17,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C17,Prices!$A$5:$A$78,0)),J17))</f>
+        <f aca="false">IF(D17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0))),CEILING(D17/INDEX(Prices!$K$5:$K$82,MATCH(C17,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C17,Prices!$A$5:$A$82,0)),J17))</f>
         <v>1.42</v>
       </c>
       <c r="L17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>78</v>
@@ -9415,7 +9810,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>0.398</v>
       </c>
       <c r="F18" s="24" t="n">
@@ -9423,7 +9818,7 @@
         <v>0.398</v>
       </c>
       <c r="G18" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H18" s="20" t="n">
@@ -9431,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C18,Prices!$A$5:$A$82,0))</f>
         <v>1.99</v>
       </c>
       <c r="J18" s="24" t="n">
@@ -9439,17 +9834,17 @@
         <v>1.99</v>
       </c>
       <c r="K18" s="24" t="n">
-        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0))),CEILING(D18/INDEX(Prices!$K$5:$K$78,MATCH(C18,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C18,Prices!$A$5:$A$78,0)),J18))</f>
+        <f aca="false">IF(D18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0))),CEILING(D18/INDEX(Prices!$K$5:$K$82,MATCH(C18,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C18,Prices!$A$5:$A$82,0)),J18))</f>
         <v>1.99</v>
       </c>
       <c r="L18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="C19" s="28" t="s">
         <v>305</v>
@@ -9458,7 +9853,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>0.398</v>
       </c>
       <c r="F19" s="24" t="n">
@@ -9466,7 +9861,7 @@
         <v>0.398</v>
       </c>
       <c r="G19" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="H19" s="20" t="n">
@@ -9474,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C19,Prices!$A$5:$A$82,0))</f>
         <v>1.99</v>
       </c>
       <c r="J19" s="24" t="n">
@@ -9482,17 +9877,17 @@
         <v>1.99</v>
       </c>
       <c r="K19" s="24" t="n">
-        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0))),CEILING(D19/INDEX(Prices!$K$5:$K$78,MATCH(C19,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C19,Prices!$A$5:$A$78,0)),J19))</f>
+        <f aca="false">IF(D19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0))),CEILING(D19/INDEX(Prices!$K$5:$K$82,MATCH(C19,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C19,Prices!$A$5:$A$82,0)),J19))</f>
         <v>1.99</v>
       </c>
       <c r="L19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="C20" s="28" t="s">
         <v>297</v>
@@ -9501,7 +9896,7 @@
         <v>0.05</v>
       </c>
       <c r="E20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>12.95</v>
       </c>
       <c r="F20" s="24" t="n">
@@ -9509,7 +9904,7 @@
         <v>0.6475</v>
       </c>
       <c r="G20" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H20" s="20" t="n">
@@ -9517,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C20,Prices!$A$5:$A$82,0))</f>
         <v>12.95</v>
       </c>
       <c r="J20" s="24" t="n">
@@ -9525,19 +9920,19 @@
         <v>12.95</v>
       </c>
       <c r="K20" s="24" t="n">
-        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0))),CEILING(D20/INDEX(Prices!$K$5:$K$78,MATCH(C20,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C20,Prices!$A$5:$A$78,0)),J20))</f>
+        <f aca="false">IF(D20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0))),CEILING(D20/INDEX(Prices!$K$5:$K$82,MATCH(C20,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C20,Prices!$A$5:$A$82,0)),J20))</f>
         <v>12.95</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="C21" s="28" t="s">
         <v>293</v>
@@ -9546,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>0.1</v>
       </c>
       <c r="F21" s="24" t="n">
@@ -9554,7 +9949,7 @@
         <v>0.1</v>
       </c>
       <c r="G21" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H21" s="20" t="n">
@@ -9562,7 +9957,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C21,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="J21" s="24" t="n">
@@ -9570,14 +9965,14 @@
         <v>1</v>
       </c>
       <c r="K21" s="24" t="n">
-        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0))),CEILING(D21/INDEX(Prices!$K$5:$K$78,MATCH(C21,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C21,Prices!$A$5:$A$78,0)),J21))</f>
+        <f aca="false">IF(D21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0))),CEILING(D21/INDEX(Prices!$K$5:$K$82,MATCH(C21,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C21,Prices!$A$5:$A$82,0)),J21))</f>
         <v>1</v>
       </c>
       <c r="L21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>314</v>
@@ -9589,7 +9984,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>0.86</v>
       </c>
       <c r="F22" s="24" t="n">
@@ -9597,7 +9992,7 @@
         <v>10.32</v>
       </c>
       <c r="G22" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H22" s="20" t="n">
@@ -9605,7 +10000,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C22,Prices!$A$5:$A$82,0))</f>
         <v>0.86</v>
       </c>
       <c r="J22" s="24" t="n">
@@ -9613,19 +10008,19 @@
         <v>10.32</v>
       </c>
       <c r="K22" s="24" t="n">
-        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0))),CEILING(D22/INDEX(Prices!$K$5:$K$78,MATCH(C22,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C22,Prices!$A$5:$A$78,0)),J22))</f>
+        <f aca="false">IF(D22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0))),CEILING(D22/INDEX(Prices!$K$5:$K$82,MATCH(C22,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C22,Prices!$A$5:$A$82,0)),J22))</f>
         <v>10.32</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="C23" s="28" t="s">
         <v>165</v>
@@ -9634,7 +10029,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>0.1425</v>
       </c>
       <c r="F23" s="24" t="n">
@@ -9642,7 +10037,7 @@
         <v>1.425</v>
       </c>
       <c r="G23" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="H23" s="20" t="n">
@@ -9650,7 +10045,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C23,Prices!$A$5:$A$82,0))</f>
         <v>5.7</v>
       </c>
       <c r="J23" s="24" t="n">
@@ -9658,26 +10053,26 @@
         <v>5.7</v>
       </c>
       <c r="K23" s="24" t="n">
-        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0))),CEILING(D23/INDEX(Prices!$K$5:$K$78,MATCH(C23,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C23,Prices!$A$5:$A$78,0)),J23))</f>
+        <f aca="false">IF(D23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0))),CEILING(D23/INDEX(Prices!$K$5:$K$82,MATCH(C23,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C23,Prices!$A$5:$A$82,0)),J23))</f>
         <v>5.7</v>
       </c>
       <c r="L23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="E24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>19.93</v>
       </c>
       <c r="F24" s="24" t="n">
@@ -9685,7 +10080,7 @@
         <v>1.993</v>
       </c>
       <c r="G24" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H24" s="20" t="n">
@@ -9693,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C24,Prices!$A$5:$A$82,0))</f>
         <v>19.93</v>
       </c>
       <c r="J24" s="24" t="n">
@@ -9701,28 +10096,28 @@
         <v>19.93</v>
       </c>
       <c r="K24" s="24" t="n">
-        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0))),CEILING(D24/INDEX(Prices!$K$5:$K$78,MATCH(C24,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C24,Prices!$A$5:$A$78,0)),J24))</f>
+        <f aca="false">IF(D24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0))),CEILING(D24/INDEX(Prices!$K$5:$K$82,MATCH(C24,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C24,Prices!$A$5:$A$82,0)),J24))</f>
         <v>19.93</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="D25" s="22" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>0.0599</v>
       </c>
       <c r="F25" s="24" t="n">
@@ -9730,7 +10125,7 @@
         <v>1.797</v>
       </c>
       <c r="G25" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="H25" s="20" t="n">
@@ -9738,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C25,Prices!$A$5:$A$82,0))</f>
         <v>5.99</v>
       </c>
       <c r="J25" s="24" t="n">
@@ -9746,26 +10141,26 @@
         <v>5.99</v>
       </c>
       <c r="K25" s="24" t="n">
-        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0))),CEILING(D25/INDEX(Prices!$K$5:$K$78,MATCH(C25,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C25,Prices!$A$5:$A$78,0)),J25))</f>
+        <f aca="false">IF(D25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0))),CEILING(D25/INDEX(Prices!$K$5:$K$82,MATCH(C25,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C25,Prices!$A$5:$A$82,0)),J25))</f>
         <v>5.99</v>
       </c>
       <c r="L25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>4.491753</v>
       </c>
       <c r="F26" s="24" t="n">
@@ -9773,7 +10168,7 @@
         <v>4.491753</v>
       </c>
       <c r="G26" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="H26" s="20" t="n">
@@ -9781,7 +10176,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C26,Prices!$A$5:$A$82,0))</f>
         <v>8.983506</v>
       </c>
       <c r="J26" s="24" t="n">
@@ -9789,17 +10184,17 @@
         <v>8.983506</v>
       </c>
       <c r="K26" s="24" t="n">
-        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0))),CEILING(D26/INDEX(Prices!$K$5:$K$78,MATCH(C26,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C26,Prices!$A$5:$A$78,0)),J26))</f>
+        <f aca="false">IF(D26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0))),CEILING(D26/INDEX(Prices!$K$5:$K$82,MATCH(C26,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C26,Prices!$A$5:$A$82,0)),J26))</f>
         <v>8.983506</v>
       </c>
       <c r="L26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="20" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C27" s="28" t="s">
         <v>148</v>
@@ -9808,7 +10203,7 @@
         <v>0.1</v>
       </c>
       <c r="E27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>12.84</v>
       </c>
       <c r="F27" s="24" t="n">
@@ -9816,7 +10211,7 @@
         <v>1.284</v>
       </c>
       <c r="G27" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H27" s="20" t="n">
@@ -9824,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C27,Prices!$A$5:$A$82,0))</f>
         <v>12.84</v>
       </c>
       <c r="J27" s="24" t="n">
@@ -9832,19 +10227,19 @@
         <v>12.84</v>
       </c>
       <c r="K27" s="24" t="n">
-        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0))),CEILING(D27/INDEX(Prices!$K$5:$K$78,MATCH(C27,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C27,Prices!$A$5:$A$78,0)),J27))</f>
+        <f aca="false">IF(D27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0))),CEILING(D27/INDEX(Prices!$K$5:$K$82,MATCH(C27,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C27,Prices!$A$5:$A$82,0)),J27))</f>
         <v>12.84</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>203</v>
@@ -9853,7 +10248,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>0.1475</v>
       </c>
       <c r="F28" s="24" t="n">
@@ -9861,7 +10256,7 @@
         <v>4.425</v>
       </c>
       <c r="G28" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>20</v>
       </c>
       <c r="H28" s="20" t="n">
@@ -9869,7 +10264,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C28,Prices!$A$5:$A$82,0))</f>
         <v>2.95</v>
       </c>
       <c r="J28" s="24" t="n">
@@ -9877,17 +10272,17 @@
         <v>5.9</v>
       </c>
       <c r="K28" s="24" t="n">
-        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0))),CEILING(D28/INDEX(Prices!$K$5:$K$78,MATCH(C28,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C28,Prices!$A$5:$A$78,0)),J28))</f>
+        <f aca="false">IF(D28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0))),CEILING(D28/INDEX(Prices!$K$5:$K$82,MATCH(C28,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C28,Prices!$A$5:$A$82,0)),J28))</f>
         <v>5.9</v>
       </c>
       <c r="L28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>207</v>
@@ -9896,7 +10291,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>0.35</v>
       </c>
       <c r="F29" s="24" t="n">
@@ -9904,7 +10299,7 @@
         <v>4.2</v>
       </c>
       <c r="G29" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H29" s="20" t="n">
@@ -9912,7 +10307,7 @@
         <v>12</v>
       </c>
       <c r="I29" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C29,Prices!$A$5:$A$82,0))</f>
         <v>0.35</v>
       </c>
       <c r="J29" s="24" t="n">
@@ -9920,17 +10315,17 @@
         <v>4.2</v>
       </c>
       <c r="K29" s="24" t="n">
-        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0))),CEILING(D29/INDEX(Prices!$K$5:$K$78,MATCH(C29,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C29,Prices!$A$5:$A$78,0)),J29))</f>
+        <f aca="false">IF(D29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0))),CEILING(D29/INDEX(Prices!$K$5:$K$82,MATCH(C29,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C29,Prices!$A$5:$A$82,0)),J29))</f>
         <v>4.2</v>
       </c>
       <c r="L29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>211</v>
@@ -9939,7 +10334,7 @@
         <v>36</v>
       </c>
       <c r="E30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>0.04</v>
       </c>
       <c r="F30" s="24" t="n">
@@ -9947,7 +10342,7 @@
         <v>1.44</v>
       </c>
       <c r="G30" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="H30" s="20" t="n">
@@ -9955,7 +10350,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C30,Prices!$A$5:$A$82,0))</f>
         <v>4</v>
       </c>
       <c r="J30" s="24" t="n">
@@ -9963,17 +10358,17 @@
         <v>4</v>
       </c>
       <c r="K30" s="24" t="n">
-        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0))),CEILING(D30/INDEX(Prices!$K$5:$K$78,MATCH(C30,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C30,Prices!$A$5:$A$78,0)),J30))</f>
+        <f aca="false">IF(D30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0))),CEILING(D30/INDEX(Prices!$K$5:$K$82,MATCH(C30,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C30,Prices!$A$5:$A$82,0)),J30))</f>
         <v>4</v>
       </c>
       <c r="L30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>240</v>
@@ -9982,7 +10377,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>0.1</v>
       </c>
       <c r="F31" s="24" t="n">
@@ -9990,7 +10385,7 @@
         <v>0.6</v>
       </c>
       <c r="G31" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>50</v>
       </c>
       <c r="H31" s="20" t="n">
@@ -9998,7 +10393,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C31,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="J31" s="24" t="n">
@@ -10006,17 +10401,17 @@
         <v>5</v>
       </c>
       <c r="K31" s="24" t="n">
-        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0))),CEILING(D31/INDEX(Prices!$K$5:$K$78,MATCH(C31,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C31,Prices!$A$5:$A$78,0)),J31))</f>
+        <f aca="false">IF(D31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0))),CEILING(D31/INDEX(Prices!$K$5:$K$82,MATCH(C31,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C31,Prices!$A$5:$A$82,0)),J31))</f>
         <v>5</v>
       </c>
       <c r="L31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>309</v>
@@ -10025,7 +10420,7 @@
         <v>28</v>
       </c>
       <c r="E32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>0.149</v>
       </c>
       <c r="F32" s="24" t="n">
@@ -10033,7 +10428,7 @@
         <v>4.172</v>
       </c>
       <c r="G32" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H32" s="20" t="n">
@@ -10041,7 +10436,7 @@
         <v>3</v>
       </c>
       <c r="I32" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C32,Prices!$A$5:$A$82,0))</f>
         <v>1.49</v>
       </c>
       <c r="J32" s="24" t="n">
@@ -10049,17 +10444,17 @@
         <v>4.47</v>
       </c>
       <c r="K32" s="24" t="n">
-        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0))),CEILING(D32/INDEX(Prices!$K$5:$K$78,MATCH(C32,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C32,Prices!$A$5:$A$78,0)),J32))</f>
+        <f aca="false">IF(D32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0))),CEILING(D32/INDEX(Prices!$K$5:$K$82,MATCH(C32,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C32,Prices!$A$5:$A$82,0)),J32))</f>
         <v>4.47</v>
       </c>
       <c r="L32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>199</v>
@@ -10068,7 +10463,7 @@
         <v>8</v>
       </c>
       <c r="E33" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>0.149</v>
       </c>
       <c r="F33" s="24" t="n">
@@ -10076,7 +10471,7 @@
         <v>1.192</v>
       </c>
       <c r="G33" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="H33" s="20" t="n">
@@ -10084,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C33,Prices!$A$5:$A$82,0))</f>
         <v>1.49</v>
       </c>
       <c r="J33" s="24" t="n">
@@ -10092,17 +10487,17 @@
         <v>1.49</v>
       </c>
       <c r="K33" s="24" t="n">
-        <f aca="false">IF(D33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C33,Prices!$A$5:$A$78,0))),CEILING(D33/INDEX(Prices!$K$5:$K$78,MATCH(C33,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C33,Prices!$A$5:$A$78,0)),J33))</f>
+        <f aca="false">IF(D33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0))),CEILING(D33/INDEX(Prices!$K$5:$K$82,MATCH(C33,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C33,Prices!$A$5:$A$82,0)),J33))</f>
         <v>1.49</v>
       </c>
       <c r="L33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="20" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>423</v>
+        <v>516</v>
       </c>
       <c r="C34" s="28" t="s">
         <v>194</v>
@@ -10111,7 +10506,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>0.07</v>
       </c>
       <c r="F34" s="24" t="n">
@@ -10119,7 +10514,7 @@
         <v>1.26</v>
       </c>
       <c r="G34" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="H34" s="20" t="n">
@@ -10127,7 +10522,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C34,Prices!$A$5:$A$82,0))</f>
         <v>7</v>
       </c>
       <c r="J34" s="24" t="n">
@@ -10135,17 +10530,17 @@
         <v>7</v>
       </c>
       <c r="K34" s="24" t="n">
-        <f aca="false">IF(D34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C34,Prices!$A$5:$A$78,0))),CEILING(D34/INDEX(Prices!$K$5:$K$78,MATCH(C34,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C34,Prices!$A$5:$A$78,0)),J34))</f>
+        <f aca="false">IF(D34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0))),CEILING(D34/INDEX(Prices!$K$5:$K$82,MATCH(C34,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C34,Prices!$A$5:$A$82,0)),J34))</f>
         <v>7</v>
       </c>
       <c r="L34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="C35" s="28" t="s">
         <v>93</v>
@@ -10154,7 +10549,7 @@
         <v>0.2</v>
       </c>
       <c r="E35" s="29" t="n">
-        <f aca="false">INDEX(Prices!$I$5:$I$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$I$5:$I$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="F35" s="24" t="n">
@@ -10162,7 +10557,7 @@
         <v>1.998</v>
       </c>
       <c r="G35" s="28" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="H35" s="20" t="n">
@@ -10170,7 +10565,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="29" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(C35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(C35,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="J35" s="24" t="n">
@@ -10178,24 +10573,24 @@
         <v>9.99</v>
       </c>
       <c r="K35" s="24" t="n">
-        <f aca="false">IF(D35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(C35,Prices!$A$5:$A$78,0))),CEILING(D35/INDEX(Prices!$K$5:$K$78,MATCH(C35,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(C35,Prices!$A$5:$A$78,0)),J35))</f>
+        <f aca="false">IF(D35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0))),CEILING(D35/INDEX(Prices!$K$5:$K$82,MATCH(C35,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(C35,Prices!$A$5:$A$82,0)),J35))</f>
         <v>9.99</v>
       </c>
       <c r="L35" s="21" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="D38" s="30" t="n">
         <v>0.4</v>
@@ -10217,15 +10612,15 @@
         <v>5.996</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D39" s="30" t="n">
         <v>34</v>
@@ -10247,7 +10642,7 @@
         <v>0.484704</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10269,7 +10664,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="F42" s="31" t="n">
         <f aca="false">F41*Summary!$C$7</f>
@@ -10320,7 +10715,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -10333,12 +10728,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10350,28 +10745,28 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10382,11 +10777,11 @@
         <v>51</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A5,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A5,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A5,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A5,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A5,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A5,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D5" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A5,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
@@ -10394,7 +10789,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A5,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A5,Prices!$A$5:$A$82,0))</f>
         <v>2.99</v>
       </c>
       <c r="G5" s="31" t="n">
@@ -10402,7 +10797,7 @@
         <v>2.99</v>
       </c>
       <c r="H5" s="31" t="n">
-        <f aca="false">IF(C5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A5,Prices!$A$5:$A$78,0))),CEILING(C5/INDEX(Prices!$K$5:$K$78,MATCH(A5,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A5,Prices!$A$5:$A$78,0)),G5))</f>
+        <f aca="false">IF(C5&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A5,Prices!$A$5:$A$82,0))),CEILING(C5/INDEX(Prices!$K$5:$K$82,MATCH(A5,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A5,Prices!$A$5:$A$82,0)),G5))</f>
         <v>2.99</v>
       </c>
     </row>
@@ -10414,11 +10809,11 @@
         <v>58</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A6,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A6,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A6,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A6,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A6,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A6,Hexapod!$D$5:$D$35)</f>
         <v>0</v>
       </c>
       <c r="D6" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A6,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
@@ -10426,7 +10821,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A6,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A6,Prices!$A$5:$A$82,0))</f>
         <v>249.99</v>
       </c>
       <c r="G6" s="31" t="n">
@@ -10434,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="31" t="n">
-        <f aca="false">IF(C6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A6,Prices!$A$5:$A$78,0))),CEILING(C6/INDEX(Prices!$K$5:$K$78,MATCH(A6,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A6,Prices!$A$5:$A$78,0)),G6))</f>
+        <f aca="false">IF(C6&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A6,Prices!$A$5:$A$82,0))),CEILING(C6/INDEX(Prices!$K$5:$K$82,MATCH(A6,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A6,Prices!$A$5:$A$82,0)),G6))</f>
         <v>0</v>
       </c>
     </row>
@@ -10446,11 +10841,11 @@
         <v>63</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A7,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A7,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A7,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A7,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A7,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A7,Hexapod!$D$5:$D$35)</f>
         <v>3</v>
       </c>
       <c r="D7" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A7,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
@@ -10458,7 +10853,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A7,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A7,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="G7" s="31" t="n">
@@ -10466,7 +10861,7 @@
         <v>2.13</v>
       </c>
       <c r="H7" s="31" t="n">
-        <f aca="false">IF(C7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A7,Prices!$A$5:$A$78,0))),CEILING(C7/INDEX(Prices!$K$5:$K$78,MATCH(A7,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A7,Prices!$A$5:$A$78,0)),G7))</f>
+        <f aca="false">IF(C7&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A7,Prices!$A$5:$A$82,0))),CEILING(C7/INDEX(Prices!$K$5:$K$82,MATCH(A7,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A7,Prices!$A$5:$A$82,0)),G7))</f>
         <v>2.13</v>
       </c>
     </row>
@@ -10478,11 +10873,11 @@
         <v>68</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A8,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A8,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A8,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A8,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A8,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A8,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D8" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A8,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E8" s="4" t="n">
@@ -10490,7 +10885,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A8,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A8,Prices!$A$5:$A$82,0))</f>
         <v>0.71</v>
       </c>
       <c r="G8" s="31" t="n">
@@ -10498,7 +10893,7 @@
         <v>0.71</v>
       </c>
       <c r="H8" s="31" t="n">
-        <f aca="false">IF(C8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A8,Prices!$A$5:$A$78,0))),CEILING(C8/INDEX(Prices!$K$5:$K$78,MATCH(A8,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A8,Prices!$A$5:$A$78,0)),G8))</f>
+        <f aca="false">IF(C8&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A8,Prices!$A$5:$A$82,0))),CEILING(C8/INDEX(Prices!$K$5:$K$82,MATCH(A8,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A8,Prices!$A$5:$A$82,0)),G8))</f>
         <v>0.71</v>
       </c>
     </row>
@@ -10510,11 +10905,11 @@
         <v>72</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A9,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A9,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A9,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A9,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A9,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A9,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D9" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A9,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E9" s="4" t="n">
@@ -10522,7 +10917,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A9,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A9,Prices!$A$5:$A$82,0))</f>
         <v>23</v>
       </c>
       <c r="G9" s="31" t="n">
@@ -10530,7 +10925,7 @@
         <v>46</v>
       </c>
       <c r="H9" s="31" t="n">
-        <f aca="false">IF(C9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A9,Prices!$A$5:$A$78,0))),CEILING(C9/INDEX(Prices!$K$5:$K$78,MATCH(A9,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A9,Prices!$A$5:$A$78,0)),G9))</f>
+        <f aca="false">IF(C9&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A9,Prices!$A$5:$A$82,0))),CEILING(C9/INDEX(Prices!$K$5:$K$82,MATCH(A9,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A9,Prices!$A$5:$A$82,0)),G9))</f>
         <v>20.961514</v>
       </c>
     </row>
@@ -10542,11 +10937,11 @@
         <v>79</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A10,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A10,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A10,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A10,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A10,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A10,Hexapod!$D$5:$D$35)</f>
         <v>4</v>
       </c>
       <c r="D10" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A10,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
@@ -10554,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A10,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A10,Prices!$A$5:$A$82,0))</f>
         <v>1.99</v>
       </c>
       <c r="G10" s="31" t="n">
@@ -10562,7 +10957,7 @@
         <v>1.99</v>
       </c>
       <c r="H10" s="31" t="n">
-        <f aca="false">IF(C10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A10,Prices!$A$5:$A$78,0))),CEILING(C10/INDEX(Prices!$K$5:$K$78,MATCH(A10,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A10,Prices!$A$5:$A$78,0)),G10))</f>
+        <f aca="false">IF(C10&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A10,Prices!$A$5:$A$82,0))),CEILING(C10/INDEX(Prices!$K$5:$K$82,MATCH(A10,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A10,Prices!$A$5:$A$82,0)),G10))</f>
         <v>1.99</v>
       </c>
     </row>
@@ -10574,11 +10969,11 @@
         <v>83</v>
       </c>
       <c r="C11" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A11,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A11,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A11,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A11,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A11,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A11,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D11" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A11,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E11" s="4" t="n">
@@ -10586,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A11,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A11,Prices!$A$5:$A$82,0))</f>
         <v>20.28985</v>
       </c>
       <c r="G11" s="31" t="n">
@@ -10594,7 +10989,7 @@
         <v>20.28985</v>
       </c>
       <c r="H11" s="31" t="n">
-        <f aca="false">IF(C11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A11,Prices!$A$5:$A$78,0))),CEILING(C11/INDEX(Prices!$K$5:$K$78,MATCH(A11,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A11,Prices!$A$5:$A$78,0)),G11))</f>
+        <f aca="false">IF(C11&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A11,Prices!$A$5:$A$82,0))),CEILING(C11/INDEX(Prices!$K$5:$K$82,MATCH(A11,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A11,Prices!$A$5:$A$82,0)),G11))</f>
         <v>20.28985</v>
       </c>
     </row>
@@ -10606,11 +11001,11 @@
         <v>89</v>
       </c>
       <c r="C12" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A12,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A12,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A12,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A12,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A12,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A12,Hexapod!$D$5:$D$35)</f>
         <v>0.5</v>
       </c>
       <c r="D12" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A12,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="E12" s="4" t="n">
@@ -10618,7 +11013,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A12,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A12,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="G12" s="31" t="n">
@@ -10626,7 +11021,7 @@
         <v>9.99</v>
       </c>
       <c r="H12" s="31" t="n">
-        <f aca="false">IF(C12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A12,Prices!$A$5:$A$78,0))),CEILING(C12/INDEX(Prices!$K$5:$K$78,MATCH(A12,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A12,Prices!$A$5:$A$78,0)),G12))</f>
+        <f aca="false">IF(C12&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A12,Prices!$A$5:$A$82,0))),CEILING(C12/INDEX(Prices!$K$5:$K$82,MATCH(A12,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A12,Prices!$A$5:$A$82,0)),G12))</f>
         <v>9.99</v>
       </c>
     </row>
@@ -10638,11 +11033,11 @@
         <v>94</v>
       </c>
       <c r="C13" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A13,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A13,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A13,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A13,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A13,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A13,Hexapod!$D$5:$D$35)</f>
         <v>0.4</v>
       </c>
       <c r="D13" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A13,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E13" s="4" t="n">
@@ -10650,7 +11045,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A13,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A13,Prices!$A$5:$A$82,0))</f>
         <v>9.99</v>
       </c>
       <c r="G13" s="31" t="n">
@@ -10658,7 +11053,7 @@
         <v>9.99</v>
       </c>
       <c r="H13" s="31" t="n">
-        <f aca="false">IF(C13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A13,Prices!$A$5:$A$78,0))),CEILING(C13/INDEX(Prices!$K$5:$K$78,MATCH(A13,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A13,Prices!$A$5:$A$78,0)),G13))</f>
+        <f aca="false">IF(C13&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A13,Prices!$A$5:$A$82,0))),CEILING(C13/INDEX(Prices!$K$5:$K$82,MATCH(A13,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A13,Prices!$A$5:$A$82,0)),G13))</f>
         <v>9.99</v>
       </c>
     </row>
@@ -10670,11 +11065,11 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A14,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A14,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A14,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A14,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A14,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A14,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D14" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A14,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="E14" s="4" t="n">
@@ -10682,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A14,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A14,Prices!$A$5:$A$82,0))</f>
         <v>6.99</v>
       </c>
       <c r="G14" s="31" t="n">
@@ -10690,7 +11085,7 @@
         <v>6.99</v>
       </c>
       <c r="H14" s="31" t="n">
-        <f aca="false">IF(C14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A14,Prices!$A$5:$A$78,0))),CEILING(C14/INDEX(Prices!$K$5:$K$78,MATCH(A14,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A14,Prices!$A$5:$A$78,0)),G14))</f>
+        <f aca="false">IF(C14&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A14,Prices!$A$5:$A$82,0))),CEILING(C14/INDEX(Prices!$K$5:$K$82,MATCH(A14,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A14,Prices!$A$5:$A$82,0)),G14))</f>
         <v>6.99</v>
       </c>
     </row>
@@ -10702,11 +11097,11 @@
         <v>102</v>
       </c>
       <c r="C15" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A15,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A15,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A15,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A15,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A15,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A15,Hexapod!$D$5:$D$35)</f>
         <v>0.2</v>
       </c>
       <c r="D15" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A15,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E15" s="4" t="n">
@@ -10714,7 +11109,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A15,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A15,Prices!$A$5:$A$82,0))</f>
         <v>11.41</v>
       </c>
       <c r="G15" s="31" t="n">
@@ -10722,7 +11117,7 @@
         <v>11.41</v>
       </c>
       <c r="H15" s="31" t="n">
-        <f aca="false">IF(C15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A15,Prices!$A$5:$A$78,0))),CEILING(C15/INDEX(Prices!$K$5:$K$78,MATCH(A15,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A15,Prices!$A$5:$A$78,0)),G15))</f>
+        <f aca="false">IF(C15&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A15,Prices!$A$5:$A$82,0))),CEILING(C15/INDEX(Prices!$K$5:$K$82,MATCH(A15,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A15,Prices!$A$5:$A$82,0)),G15))</f>
         <v>11.41</v>
       </c>
     </row>
@@ -10734,11 +11129,11 @@
         <v>106</v>
       </c>
       <c r="C16" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A16,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A16,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A16,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A16,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A16,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A16,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D16" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A16,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
@@ -10746,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A16,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A16,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="G16" s="31" t="n">
@@ -10754,7 +11149,7 @@
         <v>1.95</v>
       </c>
       <c r="H16" s="31" t="n">
-        <f aca="false">IF(C16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A16,Prices!$A$5:$A$78,0))),CEILING(C16/INDEX(Prices!$K$5:$K$78,MATCH(A16,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A16,Prices!$A$5:$A$78,0)),G16))</f>
+        <f aca="false">IF(C16&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A16,Prices!$A$5:$A$82,0))),CEILING(C16/INDEX(Prices!$K$5:$K$82,MATCH(A16,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A16,Prices!$A$5:$A$82,0)),G16))</f>
         <v>1.95</v>
       </c>
     </row>
@@ -10766,11 +11161,11 @@
         <v>111</v>
       </c>
       <c r="C17" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A17,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A17,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A17,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A17,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A17,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A17,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D17" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A17,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
@@ -10778,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A17,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A17,Prices!$A$5:$A$82,0))</f>
         <v>4.95</v>
       </c>
       <c r="G17" s="31" t="n">
@@ -10786,7 +11181,7 @@
         <v>4.95</v>
       </c>
       <c r="H17" s="31" t="n">
-        <f aca="false">IF(C17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A17,Prices!$A$5:$A$78,0))),CEILING(C17/INDEX(Prices!$K$5:$K$78,MATCH(A17,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A17,Prices!$A$5:$A$78,0)),G17))</f>
+        <f aca="false">IF(C17&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A17,Prices!$A$5:$A$82,0))),CEILING(C17/INDEX(Prices!$K$5:$K$82,MATCH(A17,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A17,Prices!$A$5:$A$82,0)),G17))</f>
         <v>4.95</v>
       </c>
     </row>
@@ -10798,11 +11193,11 @@
         <v>115</v>
       </c>
       <c r="C18" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A18,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A18,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A18,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A18,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A18,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A18,Hexapod!$D$5:$D$35)</f>
         <v>18</v>
       </c>
       <c r="D18" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A18,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
@@ -10810,7 +11205,7 @@
         <v>18</v>
       </c>
       <c r="F18" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A18,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A18,Prices!$A$5:$A$82,0))</f>
         <v>0.95</v>
       </c>
       <c r="G18" s="31" t="n">
@@ -10818,7 +11213,7 @@
         <v>17.1</v>
       </c>
       <c r="H18" s="31" t="n">
-        <f aca="false">IF(C18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A18,Prices!$A$5:$A$78,0))),CEILING(C18/INDEX(Prices!$K$5:$K$78,MATCH(A18,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A18,Prices!$A$5:$A$78,0)),G18))</f>
+        <f aca="false">IF(C18&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A18,Prices!$A$5:$A$82,0))),CEILING(C18/INDEX(Prices!$K$5:$K$82,MATCH(A18,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A18,Prices!$A$5:$A$82,0)),G18))</f>
         <v>17.1</v>
       </c>
     </row>
@@ -10830,11 +11225,11 @@
         <v>124</v>
       </c>
       <c r="C19" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A19,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A19,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A19,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A19,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A19,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A19,Hexapod!$D$5:$D$35)</f>
         <v>3</v>
       </c>
       <c r="D19" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A19,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
@@ -10842,7 +11237,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A19,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A19,Prices!$A$5:$A$82,0))</f>
         <v>9.86</v>
       </c>
       <c r="G19" s="31" t="n">
@@ -10850,7 +11245,7 @@
         <v>29.58</v>
       </c>
       <c r="H19" s="31" t="n">
-        <f aca="false">IF(C19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A19,Prices!$A$5:$A$78,0))),CEILING(C19/INDEX(Prices!$K$5:$K$78,MATCH(A19,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A19,Prices!$A$5:$A$78,0)),G19))</f>
+        <f aca="false">IF(C19&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A19,Prices!$A$5:$A$82,0))),CEILING(C19/INDEX(Prices!$K$5:$K$82,MATCH(A19,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A19,Prices!$A$5:$A$82,0)),G19))</f>
         <v>29.58</v>
       </c>
     </row>
@@ -10862,11 +11257,11 @@
         <v>129</v>
       </c>
       <c r="C20" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A20,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A20,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A20,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A20,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A20,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A20,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D20" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A20,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E20" s="4" t="n">
@@ -10874,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A20,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A20,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="G20" s="31" t="n">
@@ -10882,7 +11277,7 @@
         <v>12</v>
       </c>
       <c r="H20" s="31" t="n">
-        <f aca="false">IF(C20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A20,Prices!$A$5:$A$78,0))),CEILING(C20/INDEX(Prices!$K$5:$K$78,MATCH(A20,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A20,Prices!$A$5:$A$78,0)),G20))</f>
+        <f aca="false">IF(C20&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A20,Prices!$A$5:$A$82,0))),CEILING(C20/INDEX(Prices!$K$5:$K$82,MATCH(A20,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A20,Prices!$A$5:$A$82,0)),G20))</f>
         <v>12</v>
       </c>
     </row>
@@ -10894,11 +11289,11 @@
         <v>135</v>
       </c>
       <c r="C21" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A21,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A21,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A21,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A21,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A21,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A21,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D21" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A21,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="E21" s="4" t="n">
@@ -10906,7 +11301,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A21,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A21,Prices!$A$5:$A$82,0))</f>
         <v>13.89</v>
       </c>
       <c r="G21" s="31" t="n">
@@ -10914,7 +11309,7 @@
         <v>13.89</v>
       </c>
       <c r="H21" s="31" t="n">
-        <f aca="false">IF(C21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A21,Prices!$A$5:$A$78,0))),CEILING(C21/INDEX(Prices!$K$5:$K$78,MATCH(A21,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A21,Prices!$A$5:$A$78,0)),G21))</f>
+        <f aca="false">IF(C21&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A21,Prices!$A$5:$A$82,0))),CEILING(C21/INDEX(Prices!$K$5:$K$82,MATCH(A21,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A21,Prices!$A$5:$A$82,0)),G21))</f>
         <v>13.89</v>
       </c>
     </row>
@@ -10926,11 +11321,11 @@
         <v>144</v>
       </c>
       <c r="C22" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A22,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A22,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A22,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A22,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A22,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A22,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D22" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A22,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E22" s="4" t="n">
@@ -10938,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A22,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A22,Prices!$A$5:$A$82,0))</f>
         <v>4.93</v>
       </c>
       <c r="G22" s="31" t="n">
@@ -10946,7 +11341,7 @@
         <v>4.93</v>
       </c>
       <c r="H22" s="31" t="n">
-        <f aca="false">IF(C22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A22,Prices!$A$5:$A$78,0))),CEILING(C22/INDEX(Prices!$K$5:$K$78,MATCH(A22,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A22,Prices!$A$5:$A$78,0)),G22))</f>
+        <f aca="false">IF(C22&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A22,Prices!$A$5:$A$82,0))),CEILING(C22/INDEX(Prices!$K$5:$K$82,MATCH(A22,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A22,Prices!$A$5:$A$82,0)),G22))</f>
         <v>4.93</v>
       </c>
     </row>
@@ -10958,11 +11353,11 @@
         <v>149</v>
       </c>
       <c r="C23" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A23,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A23,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A23,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A23,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A23,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A23,Hexapod!$D$5:$D$35)</f>
         <v>0.3</v>
       </c>
       <c r="D23" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A23,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
@@ -10970,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A23,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A23,Prices!$A$5:$A$82,0))</f>
         <v>12.84</v>
       </c>
       <c r="G23" s="31" t="n">
@@ -10978,7 +11373,7 @@
         <v>12.84</v>
       </c>
       <c r="H23" s="31" t="n">
-        <f aca="false">IF(C23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A23,Prices!$A$5:$A$78,0))),CEILING(C23/INDEX(Prices!$K$5:$K$78,MATCH(A23,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A23,Prices!$A$5:$A$78,0)),G23))</f>
+        <f aca="false">IF(C23&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A23,Prices!$A$5:$A$82,0))),CEILING(C23/INDEX(Prices!$K$5:$K$82,MATCH(A23,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A23,Prices!$A$5:$A$82,0)),G23))</f>
         <v>12.84</v>
       </c>
     </row>
@@ -10990,11 +11385,11 @@
         <v>153</v>
       </c>
       <c r="C24" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A24,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A24,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A24,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A24,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A24,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A24,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D24" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A24,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
@@ -11002,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A24,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A24,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="G24" s="31" t="n">
@@ -11010,7 +11405,7 @@
         <v>1.95</v>
       </c>
       <c r="H24" s="31" t="n">
-        <f aca="false">IF(C24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A24,Prices!$A$5:$A$78,0))),CEILING(C24/INDEX(Prices!$K$5:$K$78,MATCH(A24,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A24,Prices!$A$5:$A$78,0)),G24))</f>
+        <f aca="false">IF(C24&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A24,Prices!$A$5:$A$82,0))),CEILING(C24/INDEX(Prices!$K$5:$K$82,MATCH(A24,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A24,Prices!$A$5:$A$82,0)),G24))</f>
         <v>1.95</v>
       </c>
     </row>
@@ -11022,11 +11417,11 @@
         <v>157</v>
       </c>
       <c r="C25" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A25,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A25,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A25,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A25,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A25,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A25,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D25" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A25,Prices!$A$5:$A$82,0))</f>
         <v>2</v>
       </c>
       <c r="E25" s="4" t="n">
@@ -11034,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A25,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A25,Prices!$A$5:$A$82,0))</f>
         <v>7.69</v>
       </c>
       <c r="G25" s="31" t="n">
@@ -11042,7 +11437,7 @@
         <v>7.69</v>
       </c>
       <c r="H25" s="31" t="n">
-        <f aca="false">IF(C25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A25,Prices!$A$5:$A$78,0))),CEILING(C25/INDEX(Prices!$K$5:$K$78,MATCH(A25,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A25,Prices!$A$5:$A$78,0)),G25))</f>
+        <f aca="false">IF(C25&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A25,Prices!$A$5:$A$82,0))),CEILING(C25/INDEX(Prices!$K$5:$K$82,MATCH(A25,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A25,Prices!$A$5:$A$82,0)),G25))</f>
         <v>7.69</v>
       </c>
     </row>
@@ -11054,11 +11449,11 @@
         <v>161</v>
       </c>
       <c r="C26" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A26,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A26,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A26,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A26,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A26,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A26,Hexapod!$D$5:$D$35)</f>
         <v>4</v>
       </c>
       <c r="D26" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A26,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E26" s="4" t="n">
@@ -11066,7 +11461,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A26,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A26,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="G26" s="31" t="n">
@@ -11074,7 +11469,7 @@
         <v>0.6</v>
       </c>
       <c r="H26" s="31" t="n">
-        <f aca="false">IF(C26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A26,Prices!$A$5:$A$78,0))),CEILING(C26/INDEX(Prices!$K$5:$K$78,MATCH(A26,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A26,Prices!$A$5:$A$78,0)),G26))</f>
+        <f aca="false">IF(C26&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A26,Prices!$A$5:$A$82,0))),CEILING(C26/INDEX(Prices!$K$5:$K$82,MATCH(A26,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A26,Prices!$A$5:$A$82,0)),G26))</f>
         <v>0.6</v>
       </c>
     </row>
@@ -11086,11 +11481,11 @@
         <v>166</v>
       </c>
       <c r="C27" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A27,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A27,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A27,Hexapod!$D$5:$D$35)</f>
-        <v>25</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A27,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A27,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A27,Hexapod!$D$5:$D$35)</f>
+        <v>15</v>
       </c>
       <c r="D27" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A27,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="E27" s="4" t="n">
@@ -11098,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A27,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A27,Prices!$A$5:$A$82,0))</f>
         <v>5.7</v>
       </c>
       <c r="G27" s="31" t="n">
@@ -11106,7 +11501,7 @@
         <v>5.7</v>
       </c>
       <c r="H27" s="31" t="n">
-        <f aca="false">IF(C27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A27,Prices!$A$5:$A$78,0))),CEILING(C27/INDEX(Prices!$K$5:$K$78,MATCH(A27,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A27,Prices!$A$5:$A$78,0)),G27))</f>
+        <f aca="false">IF(C27&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A27,Prices!$A$5:$A$82,0))),CEILING(C27/INDEX(Prices!$K$5:$K$82,MATCH(A27,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A27,Prices!$A$5:$A$82,0)),G27))</f>
         <v>5.7</v>
       </c>
     </row>
@@ -11118,11 +11513,11 @@
         <v>170</v>
       </c>
       <c r="C28" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A28,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A28,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A28,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A28,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A28,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A28,Hexapod!$D$5:$D$35)</f>
         <v>15</v>
       </c>
       <c r="D28" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A28,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="E28" s="4" t="n">
@@ -11130,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A28,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A28,Prices!$A$5:$A$82,0))</f>
         <v>5.7</v>
       </c>
       <c r="G28" s="31" t="n">
@@ -11138,7 +11533,7 @@
         <v>5.7</v>
       </c>
       <c r="H28" s="31" t="n">
-        <f aca="false">IF(C28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A28,Prices!$A$5:$A$78,0))),CEILING(C28/INDEX(Prices!$K$5:$K$78,MATCH(A28,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A28,Prices!$A$5:$A$78,0)),G28))</f>
+        <f aca="false">IF(C28&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A28,Prices!$A$5:$A$82,0))),CEILING(C28/INDEX(Prices!$K$5:$K$82,MATCH(A28,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A28,Prices!$A$5:$A$82,0)),G28))</f>
         <v>5.7</v>
       </c>
     </row>
@@ -11150,11 +11545,11 @@
         <v>178</v>
       </c>
       <c r="C29" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A29,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A29,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A29,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A29,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A29,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A29,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D29" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A29,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E29" s="4" t="n">
@@ -11162,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A29,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A29,Prices!$A$5:$A$82,0))</f>
         <v>15.966013</v>
       </c>
       <c r="G29" s="31" t="n">
@@ -11170,7 +11565,7 @@
         <v>15.966013</v>
       </c>
       <c r="H29" s="31" t="n">
-        <f aca="false">IF(C29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A29,Prices!$A$5:$A$78,0))),CEILING(C29/INDEX(Prices!$K$5:$K$78,MATCH(A29,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A29,Prices!$A$5:$A$78,0)),G29))</f>
+        <f aca="false">IF(C29&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A29,Prices!$A$5:$A$82,0))),CEILING(C29/INDEX(Prices!$K$5:$K$82,MATCH(A29,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A29,Prices!$A$5:$A$82,0)),G29))</f>
         <v>15.966013</v>
       </c>
     </row>
@@ -11182,11 +11577,11 @@
         <v>183</v>
       </c>
       <c r="C30" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A30,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A30,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A30,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A30,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A30,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A30,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D30" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A30,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E30" s="4" t="n">
@@ -11194,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A30,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A30,Prices!$A$5:$A$82,0))</f>
         <v>5.387305</v>
       </c>
       <c r="G30" s="31" t="n">
@@ -11202,7 +11597,7 @@
         <v>5.387305</v>
       </c>
       <c r="H30" s="31" t="n">
-        <f aca="false">IF(C30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A30,Prices!$A$5:$A$78,0))),CEILING(C30/INDEX(Prices!$K$5:$K$78,MATCH(A30,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A30,Prices!$A$5:$A$78,0)),G30))</f>
+        <f aca="false">IF(C30&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A30,Prices!$A$5:$A$82,0))),CEILING(C30/INDEX(Prices!$K$5:$K$82,MATCH(A30,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A30,Prices!$A$5:$A$82,0)),G30))</f>
         <v>5.387305</v>
       </c>
     </row>
@@ -11214,11 +11609,11 @@
         <v>187</v>
       </c>
       <c r="C31" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A31,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A31,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A31,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A31,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A31,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A31,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D31" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A31,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E31" s="4" t="n">
@@ -11226,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A31,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A31,Prices!$A$5:$A$82,0))</f>
         <v>14.97251</v>
       </c>
       <c r="G31" s="31" t="n">
@@ -11234,7 +11629,7 @@
         <v>14.97251</v>
       </c>
       <c r="H31" s="31" t="n">
-        <f aca="false">IF(C31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A31,Prices!$A$5:$A$78,0))),CEILING(C31/INDEX(Prices!$K$5:$K$78,MATCH(A31,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A31,Prices!$A$5:$A$78,0)),G31))</f>
+        <f aca="false">IF(C31&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A31,Prices!$A$5:$A$82,0))),CEILING(C31/INDEX(Prices!$K$5:$K$82,MATCH(A31,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A31,Prices!$A$5:$A$82,0)),G31))</f>
         <v>14.97251</v>
       </c>
     </row>
@@ -11246,11 +11641,11 @@
         <v>191</v>
       </c>
       <c r="C32" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A32,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A32,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A32,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A32,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A32,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A32,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D32" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A32,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E32" s="4" t="n">
@@ -11258,7 +11653,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A32,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A32,Prices!$A$5:$A$82,0))</f>
         <v>28.57</v>
       </c>
       <c r="G32" s="31" t="n">
@@ -11266,7 +11661,7 @@
         <v>28.57</v>
       </c>
       <c r="H32" s="31" t="n">
-        <f aca="false">IF(C32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A32,Prices!$A$5:$A$78,0))),CEILING(C32/INDEX(Prices!$K$5:$K$78,MATCH(A32,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A32,Prices!$A$5:$A$78,0)),G32))</f>
+        <f aca="false">IF(C32&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A32,Prices!$A$5:$A$82,0))),CEILING(C32/INDEX(Prices!$K$5:$K$82,MATCH(A32,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A32,Prices!$A$5:$A$82,0)),G32))</f>
         <v>28.57</v>
       </c>
     </row>
@@ -11278,11 +11673,11 @@
         <v>195</v>
       </c>
       <c r="C33" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A33,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A33,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A33,Hexapod!$D$5:$D$35)</f>
-        <v>25</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A33,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A33,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A33,Hexapod!$D$5:$D$35)</f>
+        <v>18</v>
       </c>
       <c r="D33" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A33,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="E33" s="4" t="n">
@@ -11290,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A33,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A33,Prices!$A$5:$A$82,0))</f>
         <v>7</v>
       </c>
       <c r="G33" s="31" t="n">
@@ -11298,7 +11693,7 @@
         <v>7</v>
       </c>
       <c r="H33" s="31" t="n">
-        <f aca="false">IF(C33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A33,Prices!$A$5:$A$78,0))),CEILING(C33/INDEX(Prices!$K$5:$K$78,MATCH(A33,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A33,Prices!$A$5:$A$78,0)),G33))</f>
+        <f aca="false">IF(C33&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A33,Prices!$A$5:$A$82,0))),CEILING(C33/INDEX(Prices!$K$5:$K$82,MATCH(A33,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A33,Prices!$A$5:$A$82,0)),G33))</f>
         <v>7</v>
       </c>
     </row>
@@ -11310,11 +11705,11 @@
         <v>200</v>
       </c>
       <c r="C34" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A34,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A34,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A34,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A34,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A34,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A34,Hexapod!$D$5:$D$35)</f>
         <v>8</v>
       </c>
       <c r="D34" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A34,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="E34" s="4" t="n">
@@ -11322,7 +11717,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A34,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A34,Prices!$A$5:$A$82,0))</f>
         <v>1.49</v>
       </c>
       <c r="G34" s="31" t="n">
@@ -11330,7 +11725,7 @@
         <v>1.49</v>
       </c>
       <c r="H34" s="31" t="n">
-        <f aca="false">IF(C34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A34,Prices!$A$5:$A$78,0))),CEILING(C34/INDEX(Prices!$K$5:$K$78,MATCH(A34,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A34,Prices!$A$5:$A$78,0)),G34))</f>
+        <f aca="false">IF(C34&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A34,Prices!$A$5:$A$82,0))),CEILING(C34/INDEX(Prices!$K$5:$K$82,MATCH(A34,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A34,Prices!$A$5:$A$82,0)),G34))</f>
         <v>1.49</v>
       </c>
     </row>
@@ -11342,11 +11737,11 @@
         <v>204</v>
       </c>
       <c r="C35" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A35,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A35,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A35,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A35,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A35,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A35,Hexapod!$D$5:$D$35)</f>
         <v>32</v>
       </c>
       <c r="D35" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A35,Prices!$A$5:$A$82,0))</f>
         <v>20</v>
       </c>
       <c r="E35" s="4" t="n">
@@ -11354,7 +11749,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A35,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A35,Prices!$A$5:$A$82,0))</f>
         <v>2.95</v>
       </c>
       <c r="G35" s="31" t="n">
@@ -11362,7 +11757,7 @@
         <v>5.9</v>
       </c>
       <c r="H35" s="31" t="n">
-        <f aca="false">IF(C35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A35,Prices!$A$5:$A$78,0))),CEILING(C35/INDEX(Prices!$K$5:$K$78,MATCH(A35,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A35,Prices!$A$5:$A$78,0)),G35))</f>
+        <f aca="false">IF(C35&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A35,Prices!$A$5:$A$82,0))),CEILING(C35/INDEX(Prices!$K$5:$K$82,MATCH(A35,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A35,Prices!$A$5:$A$82,0)),G35))</f>
         <v>5.9</v>
       </c>
     </row>
@@ -11374,11 +11769,11 @@
         <v>208</v>
       </c>
       <c r="C36" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A36,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A36,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A36,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A36,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A36,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A36,Hexapod!$D$5:$D$35)</f>
         <v>12</v>
       </c>
       <c r="D36" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A36,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A36,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E36" s="4" t="n">
@@ -11386,7 +11781,7 @@
         <v>12</v>
       </c>
       <c r="F36" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A36,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A36,Prices!$A$5:$A$82,0))</f>
         <v>0.35</v>
       </c>
       <c r="G36" s="31" t="n">
@@ -11394,7 +11789,7 @@
         <v>4.2</v>
       </c>
       <c r="H36" s="31" t="n">
-        <f aca="false">IF(C36&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A36,Prices!$A$5:$A$78,0))),CEILING(C36/INDEX(Prices!$K$5:$K$78,MATCH(A36,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A36,Prices!$A$5:$A$78,0)),G36))</f>
+        <f aca="false">IF(C36&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A36,Prices!$A$5:$A$82,0))),CEILING(C36/INDEX(Prices!$K$5:$K$82,MATCH(A36,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A36,Prices!$A$5:$A$82,0)),G36))</f>
         <v>4.2</v>
       </c>
     </row>
@@ -11406,11 +11801,11 @@
         <v>212</v>
       </c>
       <c r="C37" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A37,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A37,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A37,Hexapod!$D$5:$D$35)</f>
-        <v>36</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A37,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A37,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A37,Hexapod!$D$5:$D$35)</f>
+        <v>38</v>
       </c>
       <c r="D37" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A37,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A37,Prices!$A$5:$A$82,0))</f>
         <v>100</v>
       </c>
       <c r="E37" s="4" t="n">
@@ -11418,7 +11813,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A37,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A37,Prices!$A$5:$A$82,0))</f>
         <v>4</v>
       </c>
       <c r="G37" s="31" t="n">
@@ -11426,7 +11821,7 @@
         <v>4</v>
       </c>
       <c r="H37" s="31" t="n">
-        <f aca="false">IF(C37&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A37,Prices!$A$5:$A$78,0))),CEILING(C37/INDEX(Prices!$K$5:$K$78,MATCH(A37,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A37,Prices!$A$5:$A$78,0)),G37))</f>
+        <f aca="false">IF(C37&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A37,Prices!$A$5:$A$82,0))),CEILING(C37/INDEX(Prices!$K$5:$K$82,MATCH(A37,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A37,Prices!$A$5:$A$82,0)),G37))</f>
         <v>4</v>
       </c>
     </row>
@@ -11438,11 +11833,11 @@
         <v>217</v>
       </c>
       <c r="C38" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A38,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A38,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A38,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A38,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A38,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A38,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D38" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A38,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A38,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="E38" s="4" t="n">
@@ -11450,7 +11845,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A38,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A38,Prices!$A$5:$A$82,0))</f>
         <v>11</v>
       </c>
       <c r="G38" s="31" t="n">
@@ -11458,7 +11853,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="31" t="n">
-        <f aca="false">IF(C38&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A38,Prices!$A$5:$A$78,0))),CEILING(C38/INDEX(Prices!$K$5:$K$78,MATCH(A38,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A38,Prices!$A$5:$A$78,0)),G38))</f>
+        <f aca="false">IF(C38&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A38,Prices!$A$5:$A$82,0))),CEILING(C38/INDEX(Prices!$K$5:$K$82,MATCH(A38,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A38,Prices!$A$5:$A$82,0)),G38))</f>
         <v>11</v>
       </c>
     </row>
@@ -11470,11 +11865,11 @@
         <v>222</v>
       </c>
       <c r="C39" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A39,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A39,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A39,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A39,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A39,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A39,Hexapod!$D$5:$D$35)</f>
         <v>4</v>
       </c>
       <c r="D39" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A39,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A39,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="E39" s="4" t="n">
@@ -11482,7 +11877,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A39,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A39,Prices!$A$5:$A$82,0))</f>
         <v>12</v>
       </c>
       <c r="G39" s="31" t="n">
@@ -11490,7 +11885,7 @@
         <v>12</v>
       </c>
       <c r="H39" s="31" t="n">
-        <f aca="false">IF(C39&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A39,Prices!$A$5:$A$78,0))),CEILING(C39/INDEX(Prices!$K$5:$K$78,MATCH(A39,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A39,Prices!$A$5:$A$78,0)),G39))</f>
+        <f aca="false">IF(C39&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A39,Prices!$A$5:$A$82,0))),CEILING(C39/INDEX(Prices!$K$5:$K$82,MATCH(A39,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A39,Prices!$A$5:$A$82,0)),G39))</f>
         <v>12</v>
       </c>
     </row>
@@ -11502,11 +11897,11 @@
         <v>226</v>
       </c>
       <c r="C40" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A40,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A40,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A40,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A40,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A40,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A40,Hexapod!$D$5:$D$35)</f>
         <v>6</v>
       </c>
       <c r="D40" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A40,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A40,Prices!$A$5:$A$82,0))</f>
         <v>50</v>
       </c>
       <c r="E40" s="4" t="n">
@@ -11514,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A40,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A40,Prices!$A$5:$A$82,0))</f>
         <v>3</v>
       </c>
       <c r="G40" s="31" t="n">
@@ -11522,7 +11917,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="31" t="n">
-        <f aca="false">IF(C40&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A40,Prices!$A$5:$A$78,0))),CEILING(C40/INDEX(Prices!$K$5:$K$78,MATCH(A40,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A40,Prices!$A$5:$A$78,0)),G40))</f>
+        <f aca="false">IF(C40&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A40,Prices!$A$5:$A$82,0))),CEILING(C40/INDEX(Prices!$K$5:$K$82,MATCH(A40,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A40,Prices!$A$5:$A$82,0)),G40))</f>
         <v>3</v>
       </c>
     </row>
@@ -11534,11 +11929,11 @@
         <v>229</v>
       </c>
       <c r="C41" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A41,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A41,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A41,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A41,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A41,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A41,Hexapod!$D$5:$D$35)</f>
         <v>6</v>
       </c>
       <c r="D41" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A41,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A41,Prices!$A$5:$A$82,0))</f>
         <v>10</v>
       </c>
       <c r="E41" s="4" t="n">
@@ -11546,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A41,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A41,Prices!$A$5:$A$82,0))</f>
         <v>0.95</v>
       </c>
       <c r="G41" s="31" t="n">
@@ -11554,7 +11949,7 @@
         <v>0.95</v>
       </c>
       <c r="H41" s="31" t="n">
-        <f aca="false">IF(C41&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A41,Prices!$A$5:$A$78,0))),CEILING(C41/INDEX(Prices!$K$5:$K$78,MATCH(A41,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A41,Prices!$A$5:$A$78,0)),G41))</f>
+        <f aca="false">IF(C41&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A41,Prices!$A$5:$A$82,0))),CEILING(C41/INDEX(Prices!$K$5:$K$82,MATCH(A41,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A41,Prices!$A$5:$A$82,0)),G41))</f>
         <v>0.95</v>
       </c>
     </row>
@@ -11566,11 +11961,11 @@
         <v>233</v>
       </c>
       <c r="C42" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A42,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A42,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A42,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A42,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A42,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A42,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D42" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A42,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A42,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E42" s="4" t="n">
@@ -11578,7 +11973,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A42,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A42,Prices!$A$5:$A$82,0))</f>
         <v>0.15</v>
       </c>
       <c r="G42" s="31" t="n">
@@ -11586,7 +11981,7 @@
         <v>0.3</v>
       </c>
       <c r="H42" s="31" t="n">
-        <f aca="false">IF(C42&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A42,Prices!$A$5:$A$78,0))),CEILING(C42/INDEX(Prices!$K$5:$K$78,MATCH(A42,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A42,Prices!$A$5:$A$78,0)),G42))</f>
+        <f aca="false">IF(C42&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A42,Prices!$A$5:$A$82,0))),CEILING(C42/INDEX(Prices!$K$5:$K$82,MATCH(A42,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A42,Prices!$A$5:$A$82,0)),G42))</f>
         <v>0.3</v>
       </c>
     </row>
@@ -11598,11 +11993,11 @@
         <v>237</v>
       </c>
       <c r="C43" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A43,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A43,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A43,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A43,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A43,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A43,Hexapod!$D$5:$D$35)</f>
         <v>0.13</v>
       </c>
       <c r="D43" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A43,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A43,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E43" s="4" t="n">
@@ -11610,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A43,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A43,Prices!$A$5:$A$82,0))</f>
         <v>24</v>
       </c>
       <c r="G43" s="31" t="n">
@@ -11618,7 +12013,7 @@
         <v>24</v>
       </c>
       <c r="H43" s="31" t="n">
-        <f aca="false">IF(C43&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A43,Prices!$A$5:$A$78,0))),CEILING(C43/INDEX(Prices!$K$5:$K$78,MATCH(A43,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A43,Prices!$A$5:$A$78,0)),G43))</f>
+        <f aca="false">IF(C43&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A43,Prices!$A$5:$A$82,0))),CEILING(C43/INDEX(Prices!$K$5:$K$82,MATCH(A43,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A43,Prices!$A$5:$A$82,0)),G43))</f>
         <v>24</v>
       </c>
     </row>
@@ -11630,11 +12025,11 @@
         <v>241</v>
       </c>
       <c r="C44" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A44,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A44,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A44,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A44,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A44,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A44,Hexapod!$D$5:$D$35)</f>
         <v>11</v>
       </c>
       <c r="D44" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A44,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A44,Prices!$A$5:$A$82,0))</f>
         <v>50</v>
       </c>
       <c r="E44" s="4" t="n">
@@ -11642,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A44,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A44,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="G44" s="31" t="n">
@@ -11650,7 +12045,7 @@
         <v>5</v>
       </c>
       <c r="H44" s="31" t="n">
-        <f aca="false">IF(C44&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A44,Prices!$A$5:$A$78,0))),CEILING(C44/INDEX(Prices!$K$5:$K$78,MATCH(A44,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A44,Prices!$A$5:$A$78,0)),G44))</f>
+        <f aca="false">IF(C44&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A44,Prices!$A$5:$A$82,0))),CEILING(C44/INDEX(Prices!$K$5:$K$82,MATCH(A44,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A44,Prices!$A$5:$A$82,0)),G44))</f>
         <v>5</v>
       </c>
     </row>
@@ -11662,11 +12057,11 @@
         <v>244</v>
       </c>
       <c r="C45" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A45,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A45,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A45,Hexapod!$D$5:$D$35)</f>
-        <v>26</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A45,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A45,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A45,Hexapod!$D$5:$D$35)</f>
+        <v>38</v>
       </c>
       <c r="D45" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A45,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A45,Prices!$A$5:$A$82,0))</f>
         <v>40</v>
       </c>
       <c r="E45" s="4" t="n">
@@ -11674,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A45,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A45,Prices!$A$5:$A$82,0))</f>
         <v>1.95</v>
       </c>
       <c r="G45" s="31" t="n">
@@ -11682,7 +12077,7 @@
         <v>1.95</v>
       </c>
       <c r="H45" s="31" t="n">
-        <f aca="false">IF(C45&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A45,Prices!$A$5:$A$78,0))),CEILING(C45/INDEX(Prices!$K$5:$K$78,MATCH(A45,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A45,Prices!$A$5:$A$78,0)),G45))</f>
+        <f aca="false">IF(C45&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A45,Prices!$A$5:$A$82,0))),CEILING(C45/INDEX(Prices!$K$5:$K$82,MATCH(A45,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A45,Prices!$A$5:$A$82,0)),G45))</f>
         <v>1.95</v>
       </c>
     </row>
@@ -11694,11 +12089,11 @@
         <v>248</v>
       </c>
       <c r="C46" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A46,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A46,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A46,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A46,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A46,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A46,Hexapod!$D$5:$D$35)</f>
         <v>20</v>
       </c>
       <c r="D46" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A46,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A46,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E46" s="4" t="n">
@@ -11706,7 +12101,7 @@
         <v>20</v>
       </c>
       <c r="F46" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A46,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A46,Prices!$A$5:$A$82,0))</f>
         <v>6</v>
       </c>
       <c r="G46" s="31" t="n">
@@ -11714,7 +12109,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="31" t="n">
-        <f aca="false">IF(C46&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A46,Prices!$A$5:$A$78,0))),CEILING(C46/INDEX(Prices!$K$5:$K$78,MATCH(A46,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A46,Prices!$A$5:$A$78,0)),G46))</f>
+        <f aca="false">IF(C46&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A46,Prices!$A$5:$A$82,0))),CEILING(C46/INDEX(Prices!$K$5:$K$82,MATCH(A46,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A46,Prices!$A$5:$A$82,0)),G46))</f>
         <v>64.3678</v>
       </c>
     </row>
@@ -11726,11 +12121,11 @@
         <v>253</v>
       </c>
       <c r="C47" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A47,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A47,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A47,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A47,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A47,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A47,Hexapod!$D$5:$D$35)</f>
         <v>3</v>
       </c>
       <c r="D47" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A47,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A47,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E47" s="4" t="n">
@@ -11738,7 +12133,7 @@
         <v>3</v>
       </c>
       <c r="F47" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A47,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A47,Prices!$A$5:$A$82,0))</f>
         <v>8.95</v>
       </c>
       <c r="G47" s="31" t="n">
@@ -11746,7 +12141,7 @@
         <v>26.85</v>
       </c>
       <c r="H47" s="31" t="n">
-        <f aca="false">IF(C47&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A47,Prices!$A$5:$A$78,0))),CEILING(C47/INDEX(Prices!$K$5:$K$78,MATCH(A47,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A47,Prices!$A$5:$A$78,0)),G47))</f>
+        <f aca="false">IF(C47&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A47,Prices!$A$5:$A$82,0))),CEILING(C47/INDEX(Prices!$K$5:$K$82,MATCH(A47,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A47,Prices!$A$5:$A$82,0)),G47))</f>
         <v>20.947521</v>
       </c>
     </row>
@@ -11758,11 +12153,11 @@
         <v>259</v>
       </c>
       <c r="C48" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A48,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A48,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A48,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A48,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A48,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A48,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D48" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A48,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A48,Prices!$A$5:$A$82,0))</f>
         <v>5</v>
       </c>
       <c r="E48" s="4" t="n">
@@ -11770,7 +12165,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A48,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A48,Prices!$A$5:$A$82,0))</f>
         <v>8.325835</v>
       </c>
       <c r="G48" s="31" t="n">
@@ -11778,7 +12173,7 @@
         <v>8.325835</v>
       </c>
       <c r="H48" s="31" t="n">
-        <f aca="false">IF(C48&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A48,Prices!$A$5:$A$78,0))),CEILING(C48/INDEX(Prices!$K$5:$K$78,MATCH(A48,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A48,Prices!$A$5:$A$78,0)),G48))</f>
+        <f aca="false">IF(C48&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A48,Prices!$A$5:$A$82,0))),CEILING(C48/INDEX(Prices!$K$5:$K$82,MATCH(A48,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A48,Prices!$A$5:$A$82,0)),G48))</f>
         <v>8.325835</v>
       </c>
     </row>
@@ -11790,11 +12185,11 @@
         <v>264</v>
       </c>
       <c r="C49" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A49,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A49,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A49,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A49,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A49,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A49,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D49" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A49,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A49,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E49" s="4" t="n">
@@ -11802,7 +12197,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A49,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A49,Prices!$A$5:$A$82,0))</f>
         <v>7.99</v>
       </c>
       <c r="G49" s="31" t="n">
@@ -11810,7 +12205,7 @@
         <v>15.98</v>
       </c>
       <c r="H49" s="31" t="n">
-        <f aca="false">IF(C49&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A49,Prices!$A$5:$A$78,0))),CEILING(C49/INDEX(Prices!$K$5:$K$78,MATCH(A49,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A49,Prices!$A$5:$A$78,0)),G49))</f>
+        <f aca="false">IF(C49&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A49,Prices!$A$5:$A$82,0))),CEILING(C49/INDEX(Prices!$K$5:$K$82,MATCH(A49,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A49,Prices!$A$5:$A$82,0)),G49))</f>
         <v>15.98</v>
       </c>
     </row>
@@ -11822,11 +12217,11 @@
         <v>268</v>
       </c>
       <c r="C50" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A50,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A50,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A50,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A50,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A50,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A50,Hexapod!$D$5:$D$35)</f>
         <v>2</v>
       </c>
       <c r="D50" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A50,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A50,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E50" s="4" t="n">
@@ -11834,7 +12229,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A50,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A50,Prices!$A$5:$A$82,0))</f>
         <v>6.95</v>
       </c>
       <c r="G50" s="31" t="n">
@@ -11842,23 +12237,23 @@
         <v>13.9</v>
       </c>
       <c r="H50" s="31" t="n">
-        <f aca="false">IF(C50&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A50,Prices!$A$5:$A$78,0))),CEILING(C50/INDEX(Prices!$K$5:$K$78,MATCH(A50,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A50,Prices!$A$5:$A$78,0)),G50))</f>
+        <f aca="false">IF(C50&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A50,Prices!$A$5:$A$82,0))),CEILING(C50/INDEX(Prices!$K$5:$K$82,MATCH(A50,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A50,Prices!$A$5:$A$82,0)),G50))</f>
         <v>13.9</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="35" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C51" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A51,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A51,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A51,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A51,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A51,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A51,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D51" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A51,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A51,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E51" s="4" t="n">
@@ -11866,31 +12261,31 @@
         <v>1</v>
       </c>
       <c r="F51" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A51,Prices!$A$5:$A$78,0))</f>
-        <v>18.16</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A51,Prices!$A$5:$A$82,0))</f>
+        <v>27.13</v>
       </c>
       <c r="G51" s="31" t="n">
         <f aca="false">E51*F51</f>
-        <v>18.16</v>
+        <v>27.13</v>
       </c>
       <c r="H51" s="31" t="n">
-        <f aca="false">IF(C51&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A51,Prices!$A$5:$A$78,0))),CEILING(C51/INDEX(Prices!$K$5:$K$78,MATCH(A51,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A51,Prices!$A$5:$A$78,0)),G51))</f>
-        <v>18.16</v>
+        <f aca="false">IF(C51&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A51,Prices!$A$5:$A$82,0))),CEILING(C51/INDEX(Prices!$K$5:$K$82,MATCH(A51,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A51,Prices!$A$5:$A$82,0)),G51))</f>
+        <v>27.13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="35" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C52" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A52,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A52,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A52,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A52,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A52,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A52,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D52" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A52,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A52,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E52" s="4" t="n">
@@ -11898,319 +12293,319 @@
         <v>1</v>
       </c>
       <c r="F52" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A52,Prices!$A$5:$A$78,0))</f>
-        <v>27.13</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A52,Prices!$A$5:$A$82,0))</f>
+        <v>0.99</v>
       </c>
       <c r="G52" s="31" t="n">
         <f aca="false">E52*F52</f>
-        <v>27.13</v>
+        <v>0.99</v>
       </c>
       <c r="H52" s="31" t="n">
-        <f aca="false">IF(C52&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A52,Prices!$A$5:$A$78,0))),CEILING(C52/INDEX(Prices!$K$5:$K$78,MATCH(A52,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A52,Prices!$A$5:$A$78,0)),G52))</f>
-        <v>27.13</v>
+        <f aca="false">IF(C52&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A52,Prices!$A$5:$A$82,0))),CEILING(C52/INDEX(Prices!$K$5:$K$82,MATCH(A52,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A52,Prices!$A$5:$A$82,0)),G52))</f>
+        <v>0.99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="35" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C53" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A53,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A53,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A53,Hexapod!$D$5:$D$35)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A53,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A53,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A53,Hexapod!$D$5:$D$35)</f>
+        <v>2</v>
       </c>
       <c r="D53" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A53,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A53,Prices!$A$5:$A$82,0))</f>
+        <v>10</v>
       </c>
       <c r="E53" s="4" t="n">
         <f aca="false">IF(C53&lt;=0,0,CEILING(C53/D53,1))</f>
         <v>1</v>
       </c>
       <c r="F53" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A53,Prices!$A$5:$A$78,0))</f>
-        <v>0.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A53,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="G53" s="31" t="n">
         <f aca="false">E53*F53</f>
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H53" s="31" t="n">
-        <f aca="false">IF(C53&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A53,Prices!$A$5:$A$78,0))),CEILING(C53/INDEX(Prices!$K$5:$K$78,MATCH(A53,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A53,Prices!$A$5:$A$78,0)),G53))</f>
-        <v>0.99</v>
+        <f aca="false">IF(C53&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A53,Prices!$A$5:$A$82,0))),CEILING(C53/INDEX(Prices!$K$5:$K$82,MATCH(A53,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A53,Prices!$A$5:$A$82,0)),G53))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="35" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C54" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A54,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A54,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A54,Hexapod!$D$5:$D$35)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A54,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A54,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A54,Hexapod!$D$5:$D$35)</f>
+        <v>0.25</v>
       </c>
       <c r="D54" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A54,Prices!$A$5:$A$78,0))</f>
-        <v>10</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A54,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
         <f aca="false">IF(C54&lt;=0,0,CEILING(C54/D54,1))</f>
         <v>1</v>
       </c>
       <c r="F54" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A54,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A54,Prices!$A$5:$A$82,0))</f>
+        <v>12.95</v>
       </c>
       <c r="G54" s="31" t="n">
         <f aca="false">E54*F54</f>
-        <v>1</v>
+        <v>12.95</v>
       </c>
       <c r="H54" s="31" t="n">
-        <f aca="false">IF(C54&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A54,Prices!$A$5:$A$78,0))),CEILING(C54/INDEX(Prices!$K$5:$K$78,MATCH(A54,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A54,Prices!$A$5:$A$78,0)),G54))</f>
-        <v>1</v>
+        <f aca="false">IF(C54&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A54,Prices!$A$5:$A$82,0))),CEILING(C54/INDEX(Prices!$K$5:$K$82,MATCH(A54,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A54,Prices!$A$5:$A$82,0)),G54))</f>
+        <v>12.95</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C55" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A55,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A55,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A55,Hexapod!$D$5:$D$35)</f>
-        <v>0.25</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A55,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A55,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A55,Hexapod!$D$5:$D$35)</f>
+        <v>4</v>
       </c>
       <c r="D55" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A55,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A55,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
       </c>
       <c r="E55" s="4" t="n">
         <f aca="false">IF(C55&lt;=0,0,CEILING(C55/D55,1))</f>
         <v>1</v>
       </c>
       <c r="F55" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A55,Prices!$A$5:$A$78,0))</f>
-        <v>12.95</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A55,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="G55" s="31" t="n">
         <f aca="false">E55*F55</f>
-        <v>12.95</v>
+        <v>1</v>
       </c>
       <c r="H55" s="31" t="n">
-        <f aca="false">IF(C55&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A55,Prices!$A$5:$A$78,0))),CEILING(C55/INDEX(Prices!$K$5:$K$78,MATCH(A55,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A55,Prices!$A$5:$A$78,0)),G55))</f>
-        <v>12.95</v>
+        <f aca="false">IF(C55&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A55,Prices!$A$5:$A$82,0))),CEILING(C55/INDEX(Prices!$K$5:$K$82,MATCH(A55,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A55,Prices!$A$5:$A$82,0)),G55))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="35" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C56" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A56,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A56,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A56,Hexapod!$D$5:$D$35)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A56,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A56,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A56,Hexapod!$D$5:$D$35)</f>
+        <v>2</v>
       </c>
       <c r="D56" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A56,Prices!$A$5:$A$78,0))</f>
-        <v>4</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A56,Prices!$A$5:$A$82,0))</f>
+        <v>5</v>
       </c>
       <c r="E56" s="4" t="n">
         <f aca="false">IF(C56&lt;=0,0,CEILING(C56/D56,1))</f>
         <v>1</v>
       </c>
       <c r="F56" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A56,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A56,Prices!$A$5:$A$82,0))</f>
+        <v>1.99</v>
       </c>
       <c r="G56" s="31" t="n">
         <f aca="false">E56*F56</f>
-        <v>1</v>
+        <v>1.99</v>
       </c>
       <c r="H56" s="31" t="n">
-        <f aca="false">IF(C56&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A56,Prices!$A$5:$A$78,0))),CEILING(C56/INDEX(Prices!$K$5:$K$78,MATCH(A56,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A56,Prices!$A$5:$A$78,0)),G56))</f>
-        <v>1</v>
+        <f aca="false">IF(C56&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A56,Prices!$A$5:$A$82,0))),CEILING(C56/INDEX(Prices!$K$5:$K$82,MATCH(A56,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A56,Prices!$A$5:$A$82,0)),G56))</f>
+        <v>1.99</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="35" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C57" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A57,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A57,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A57,Hexapod!$D$5:$D$35)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A57,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A57,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A57,Hexapod!$D$5:$D$35)</f>
+        <v>61</v>
       </c>
       <c r="D57" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A57,Prices!$A$5:$A$78,0))</f>
-        <v>5</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A57,Prices!$A$5:$A$82,0))</f>
+        <v>10</v>
       </c>
       <c r="E57" s="4" t="n">
         <f aca="false">IF(C57&lt;=0,0,CEILING(C57/D57,1))</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F57" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A57,Prices!$A$5:$A$78,0))</f>
-        <v>1.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A57,Prices!$A$5:$A$82,0))</f>
+        <v>1.49</v>
       </c>
       <c r="G57" s="31" t="n">
         <f aca="false">E57*F57</f>
-        <v>1.99</v>
+        <v>10.43</v>
       </c>
       <c r="H57" s="31" t="n">
-        <f aca="false">IF(C57&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A57,Prices!$A$5:$A$78,0))),CEILING(C57/INDEX(Prices!$K$5:$K$78,MATCH(A57,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A57,Prices!$A$5:$A$78,0)),G57))</f>
-        <v>1.99</v>
+        <f aca="false">IF(C57&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A57,Prices!$A$5:$A$82,0))),CEILING(C57/INDEX(Prices!$K$5:$K$82,MATCH(A57,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A57,Prices!$A$5:$A$82,0)),G57))</f>
+        <v>10.43</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="35" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C58" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A58,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A58,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A58,Hexapod!$D$5:$D$35)</f>
-        <v>42</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A58,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A58,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A58,Hexapod!$D$5:$D$35)</f>
+        <v>12</v>
       </c>
       <c r="D58" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A58,Prices!$A$5:$A$78,0))</f>
-        <v>10</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A58,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="E58" s="4" t="n">
         <f aca="false">IF(C58&lt;=0,0,CEILING(C58/D58,1))</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F58" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A58,Prices!$A$5:$A$78,0))</f>
-        <v>1.49</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A58,Prices!$A$5:$A$82,0))</f>
+        <v>0.86</v>
       </c>
       <c r="G58" s="31" t="n">
         <f aca="false">E58*F58</f>
-        <v>7.45</v>
+        <v>10.32</v>
       </c>
       <c r="H58" s="31" t="n">
-        <f aca="false">IF(C58&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A58,Prices!$A$5:$A$78,0))),CEILING(C58/INDEX(Prices!$K$5:$K$78,MATCH(A58,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A58,Prices!$A$5:$A$78,0)),G58))</f>
-        <v>7.45</v>
+        <f aca="false">IF(C58&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A58,Prices!$A$5:$A$82,0))),CEILING(C58/INDEX(Prices!$K$5:$K$82,MATCH(A58,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A58,Prices!$A$5:$A$82,0)),G58))</f>
+        <v>10.32</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="35" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C59" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A59,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A59,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A59,Hexapod!$D$5:$D$35)</f>
-        <v>12</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A59,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A59,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A59,Hexapod!$D$5:$D$35)</f>
+        <v>1</v>
       </c>
       <c r="D59" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A59,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A59,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
         <f aca="false">IF(C59&lt;=0,0,CEILING(C59/D59,1))</f>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F59" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A59,Prices!$A$5:$A$78,0))</f>
-        <v>0.86</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A59,Prices!$A$5:$A$82,0))</f>
+        <v>3.06</v>
       </c>
       <c r="G59" s="31" t="n">
         <f aca="false">E59*F59</f>
-        <v>10.32</v>
+        <v>3.06</v>
       </c>
       <c r="H59" s="31" t="n">
-        <f aca="false">IF(C59&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A59,Prices!$A$5:$A$78,0))),CEILING(C59/INDEX(Prices!$K$5:$K$78,MATCH(A59,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A59,Prices!$A$5:$A$78,0)),G59))</f>
-        <v>10.32</v>
+        <f aca="false">IF(C59&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A59,Prices!$A$5:$A$82,0))),CEILING(C59/INDEX(Prices!$K$5:$K$82,MATCH(A59,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A59,Prices!$A$5:$A$82,0)),G59))</f>
+        <v>3.06</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="35" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C60" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A60,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A60,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A60,Hexapod!$D$5:$D$35)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A60,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A60,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A60,Hexapod!$D$5:$D$35)</f>
+        <v>2</v>
       </c>
       <c r="D60" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A60,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A60,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E60" s="4" t="n">
         <f aca="false">IF(C60&lt;=0,0,CEILING(C60/D60,1))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A60,Prices!$A$5:$A$78,0))</f>
-        <v>3.06</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A60,Prices!$A$5:$A$82,0))</f>
+        <v>1.36</v>
       </c>
       <c r="G60" s="31" t="n">
         <f aca="false">E60*F60</f>
-        <v>3.06</v>
+        <v>2.72</v>
       </c>
       <c r="H60" s="31" t="n">
-        <f aca="false">IF(C60&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A60,Prices!$A$5:$A$78,0))),CEILING(C60/INDEX(Prices!$K$5:$K$78,MATCH(A60,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A60,Prices!$A$5:$A$78,0)),G60))</f>
-        <v>3.06</v>
+        <f aca="false">IF(C60&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A60,Prices!$A$5:$A$82,0))),CEILING(C60/INDEX(Prices!$K$5:$K$82,MATCH(A60,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A60,Prices!$A$5:$A$82,0)),G60))</f>
+        <v>2.72</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="35" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C61" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A61,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A61,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A61,Hexapod!$D$5:$D$35)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A61,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A61,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A61,Hexapod!$D$5:$D$35)</f>
+        <v>1</v>
       </c>
       <c r="D61" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A61,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A61,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E61" s="4" t="n">
         <f aca="false">IF(C61&lt;=0,0,CEILING(C61/D61,1))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A61,Prices!$A$5:$A$78,0))</f>
-        <v>1.36</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A61,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="G61" s="31" t="n">
         <f aca="false">E61*F61</f>
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="H61" s="31" t="n">
-        <f aca="false">IF(C61&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A61,Prices!$A$5:$A$78,0))),CEILING(C61/INDEX(Prices!$K$5:$K$78,MATCH(A61,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A61,Prices!$A$5:$A$78,0)),G61))</f>
-        <v>2.72</v>
+        <f aca="false">IF(C61&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A61,Prices!$A$5:$A$82,0))),CEILING(C61/INDEX(Prices!$K$5:$K$82,MATCH(A61,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A61,Prices!$A$5:$A$82,0)),G61))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="35" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C62" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A62,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A62,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A62,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A62,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A62,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A62,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D62" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A62,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A62,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E62" s="4" t="n">
@@ -12218,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A62,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A62,Prices!$A$5:$A$82,0))</f>
         <v>3.99</v>
       </c>
       <c r="G62" s="31" t="n">
@@ -12226,23 +12621,23 @@
         <v>3.99</v>
       </c>
       <c r="H62" s="31" t="n">
-        <f aca="false">IF(C62&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A62,Prices!$A$5:$A$78,0))),CEILING(C62/INDEX(Prices!$K$5:$K$78,MATCH(A62,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A62,Prices!$A$5:$A$78,0)),G62))</f>
+        <f aca="false">IF(C62&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A62,Prices!$A$5:$A$82,0))),CEILING(C62/INDEX(Prices!$K$5:$K$82,MATCH(A62,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A62,Prices!$A$5:$A$82,0)),G62))</f>
         <v>3.99</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="35" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C63" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A63,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A63,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A63,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A63,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A63,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A63,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D63" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A63,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A63,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
@@ -12250,7 +12645,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A63,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A63,Prices!$A$5:$A$82,0))</f>
         <v>7.07</v>
       </c>
       <c r="G63" s="31" t="n">
@@ -12258,23 +12653,23 @@
         <v>7.07</v>
       </c>
       <c r="H63" s="31" t="n">
-        <f aca="false">IF(C63&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A63,Prices!$A$5:$A$78,0))),CEILING(C63/INDEX(Prices!$K$5:$K$78,MATCH(A63,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A63,Prices!$A$5:$A$78,0)),G63))</f>
+        <f aca="false">IF(C63&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A63,Prices!$A$5:$A$82,0))),CEILING(C63/INDEX(Prices!$K$5:$K$82,MATCH(A63,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A63,Prices!$A$5:$A$82,0)),G63))</f>
         <v>7.07</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="35" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C64" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A64,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A64,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A64,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A64,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A64,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A64,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D64" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A64,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A64,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
@@ -12282,7 +12677,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A64,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A64,Prices!$A$5:$A$82,0))</f>
         <v>3</v>
       </c>
       <c r="G64" s="31" t="n">
@@ -12290,55 +12685,55 @@
         <v>3</v>
       </c>
       <c r="H64" s="31" t="n">
-        <f aca="false">IF(C64&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A64,Prices!$A$5:$A$78,0))),CEILING(C64/INDEX(Prices!$K$5:$K$78,MATCH(A64,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A64,Prices!$A$5:$A$78,0)),G64))</f>
+        <f aca="false">IF(C64&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A64,Prices!$A$5:$A$82,0))),CEILING(C64/INDEX(Prices!$K$5:$K$82,MATCH(A64,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A64,Prices!$A$5:$A$82,0)),G64))</f>
         <v>3</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="35" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C65" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A65,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A65,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A65,Hexapod!$D$5:$D$35)</f>
-        <v>1</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A65,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A65,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A65,Hexapod!$D$5:$D$35)</f>
+        <v>2</v>
       </c>
       <c r="D65" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A65,Prices!$A$5:$A$78,0))</f>
-        <v>1</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A65,Prices!$A$5:$A$82,0))</f>
+        <v>10</v>
       </c>
       <c r="E65" s="4" t="n">
         <f aca="false">IF(C65&lt;=0,0,CEILING(C65/D65,1))</f>
         <v>1</v>
       </c>
       <c r="F65" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A65,Prices!$A$5:$A$78,0))</f>
-        <v>2.29</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A65,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
       </c>
       <c r="G65" s="31" t="n">
         <f aca="false">E65*F65</f>
-        <v>2.29</v>
+        <v>4</v>
       </c>
       <c r="H65" s="31" t="n">
-        <f aca="false">IF(C65&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A65,Prices!$A$5:$A$78,0))),CEILING(C65/INDEX(Prices!$K$5:$K$78,MATCH(A65,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A65,Prices!$A$5:$A$78,0)),G65))</f>
-        <v>2.29</v>
+        <f aca="false">IF(C65&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A65,Prices!$A$5:$A$82,0))),CEILING(C65/INDEX(Prices!$K$5:$K$82,MATCH(A65,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A65,Prices!$A$5:$A$82,0)),G65))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="35" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C66" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A66,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A66,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A66,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A66,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A66,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A66,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D66" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A66,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A66,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E66" s="4" t="n">
@@ -12346,31 +12741,31 @@
         <v>1</v>
       </c>
       <c r="F66" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A66,Prices!$A$5:$A$78,0))</f>
-        <v>0.72</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A66,Prices!$A$5:$A$82,0))</f>
+        <v>2.29</v>
       </c>
       <c r="G66" s="31" t="n">
         <f aca="false">E66*F66</f>
-        <v>0.72</v>
+        <v>2.29</v>
       </c>
       <c r="H66" s="31" t="n">
-        <f aca="false">IF(C66&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A66,Prices!$A$5:$A$78,0))),CEILING(C66/INDEX(Prices!$K$5:$K$78,MATCH(A66,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A66,Prices!$A$5:$A$78,0)),G66))</f>
-        <v>0.72</v>
+        <f aca="false">IF(C66&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A66,Prices!$A$5:$A$82,0))),CEILING(C66/INDEX(Prices!$K$5:$K$82,MATCH(A66,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A66,Prices!$A$5:$A$82,0)),G66))</f>
+        <v>2.29</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="35" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C67" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A67,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A67,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A67,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A67,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A67,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A67,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D67" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A67,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A67,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
@@ -12378,31 +12773,31 @@
         <v>1</v>
       </c>
       <c r="F67" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A67,Prices!$A$5:$A$78,0))</f>
-        <v>34.968507</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A67,Prices!$A$5:$A$82,0))</f>
+        <v>0.72</v>
       </c>
       <c r="G67" s="31" t="n">
         <f aca="false">E67*F67</f>
-        <v>34.968507</v>
+        <v>0.72</v>
       </c>
       <c r="H67" s="31" t="n">
-        <f aca="false">IF(C67&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A67,Prices!$A$5:$A$78,0))),CEILING(C67/INDEX(Prices!$K$5:$K$78,MATCH(A67,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A67,Prices!$A$5:$A$78,0)),G67))</f>
-        <v>34.968507</v>
+        <f aca="false">IF(C67&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A67,Prices!$A$5:$A$82,0))),CEILING(C67/INDEX(Prices!$K$5:$K$82,MATCH(A67,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A67,Prices!$A$5:$A$82,0)),G67))</f>
+        <v>0.72</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="35" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C68" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A68,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A68,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A68,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A68,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A68,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A68,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D68" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A68,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A68,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E68" s="4" t="n">
@@ -12410,63 +12805,63 @@
         <v>1</v>
       </c>
       <c r="F68" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A68,Prices!$A$5:$A$78,0))</f>
-        <v>15</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A68,Prices!$A$5:$A$82,0))</f>
+        <v>34.968507</v>
       </c>
       <c r="G68" s="31" t="n">
         <f aca="false">E68*F68</f>
-        <v>15</v>
+        <v>34.968507</v>
       </c>
       <c r="H68" s="31" t="n">
-        <f aca="false">IF(C68&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A68,Prices!$A$5:$A$78,0))),CEILING(C68/INDEX(Prices!$K$5:$K$78,MATCH(A68,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A68,Prices!$A$5:$A$78,0)),G68))</f>
-        <v>15</v>
+        <f aca="false">IF(C68&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A68,Prices!$A$5:$A$82,0))),CEILING(C68/INDEX(Prices!$K$5:$K$82,MATCH(A68,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A68,Prices!$A$5:$A$82,0)),G68))</f>
+        <v>34.968507</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="35" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C69" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A69,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A69,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A69,Hexapod!$D$5:$D$35)</f>
-        <v>2</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A69,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A69,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A69,Hexapod!$D$5:$D$35)</f>
+        <v>1</v>
       </c>
       <c r="D69" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A69,Prices!$A$5:$A$78,0))</f>
-        <v>2</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A69,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="E69" s="4" t="n">
         <f aca="false">IF(C69&lt;=0,0,CEILING(C69/D69,1))</f>
         <v>1</v>
       </c>
       <c r="F69" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A69,Prices!$A$5:$A$78,0))</f>
-        <v>8.983506</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A69,Prices!$A$5:$A$82,0))</f>
+        <v>15</v>
       </c>
       <c r="G69" s="31" t="n">
         <f aca="false">E69*F69</f>
-        <v>8.983506</v>
+        <v>15</v>
       </c>
       <c r="H69" s="31" t="n">
-        <f aca="false">IF(C69&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A69,Prices!$A$5:$A$78,0))),CEILING(C69/INDEX(Prices!$K$5:$K$78,MATCH(A69,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A69,Prices!$A$5:$A$78,0)),G69))</f>
-        <v>8.983506</v>
+        <f aca="false">IF(C69&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A69,Prices!$A$5:$A$82,0))),CEILING(C69/INDEX(Prices!$K$5:$K$82,MATCH(A69,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A69,Prices!$A$5:$A$82,0)),G69))</f>
+        <v>15</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="35" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C70" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A70,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A70,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A70,Hexapod!$D$5:$D$35)</f>
-        <v>0.2</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A70,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A70,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A70,Hexapod!$D$5:$D$35)</f>
+        <v>1</v>
       </c>
       <c r="D70" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A70,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A70,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E70" s="4" t="n">
@@ -12474,63 +12869,63 @@
         <v>1</v>
       </c>
       <c r="F70" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A70,Prices!$A$5:$A$78,0))</f>
-        <v>19.93</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A70,Prices!$A$5:$A$82,0))</f>
+        <v>8</v>
       </c>
       <c r="G70" s="31" t="n">
         <f aca="false">E70*F70</f>
-        <v>19.93</v>
+        <v>8</v>
       </c>
       <c r="H70" s="31" t="n">
-        <f aca="false">IF(C70&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A70,Prices!$A$5:$A$78,0))),CEILING(C70/INDEX(Prices!$K$5:$K$78,MATCH(A70,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A70,Prices!$A$5:$A$78,0)),G70))</f>
-        <v>19.93</v>
+        <f aca="false">IF(C70&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A70,Prices!$A$5:$A$82,0))),CEILING(C70/INDEX(Prices!$K$5:$K$82,MATCH(A70,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A70,Prices!$A$5:$A$82,0)),G70))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C71" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A71,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A71,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A71,Hexapod!$D$5:$D$35)</f>
-        <v>4</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A71,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A71,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A71,Hexapod!$D$5:$D$35)</f>
+        <v>2</v>
       </c>
       <c r="D71" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A71,Prices!$A$5:$A$78,0))</f>
-        <v>25</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A71,Prices!$A$5:$A$82,0))</f>
+        <v>2</v>
       </c>
       <c r="E71" s="4" t="n">
         <f aca="false">IF(C71&lt;=0,0,CEILING(C71/D71,1))</f>
         <v>1</v>
       </c>
       <c r="F71" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A71,Prices!$A$5:$A$78,0))</f>
-        <v>4</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A71,Prices!$A$5:$A$82,0))</f>
+        <v>8.983506</v>
       </c>
       <c r="G71" s="31" t="n">
         <f aca="false">E71*F71</f>
-        <v>4</v>
+        <v>8.983506</v>
       </c>
       <c r="H71" s="31" t="n">
-        <f aca="false">IF(C71&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A71,Prices!$A$5:$A$78,0))),CEILING(C71/INDEX(Prices!$K$5:$K$78,MATCH(A71,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A71,Prices!$A$5:$A$78,0)),G71))</f>
-        <v>4</v>
+        <f aca="false">IF(C71&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A71,Prices!$A$5:$A$82,0))),CEILING(C71/INDEX(Prices!$K$5:$K$82,MATCH(A71,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A71,Prices!$A$5:$A$82,0)),G71))</f>
+        <v>8.983506</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="35" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C72" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A72,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A72,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A72,Hexapod!$D$5:$D$35)</f>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A72,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A72,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A72,Hexapod!$D$5:$D$35)</f>
         <v>1</v>
       </c>
       <c r="D72" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A72,Prices!$A$5:$A$78,0))</f>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A72,Prices!$A$5:$A$82,0))</f>
         <v>1</v>
       </c>
       <c r="E72" s="4" t="n">
@@ -12538,16 +12933,16 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A72,Prices!$A$5:$A$78,0))</f>
-        <v>2.770614</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A72,Prices!$A$5:$A$82,0))</f>
+        <v>6</v>
       </c>
       <c r="G72" s="31" t="n">
         <f aca="false">E72*F72</f>
-        <v>2.770614</v>
+        <v>6</v>
       </c>
       <c r="H72" s="31" t="n">
-        <f aca="false">IF(C72&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A72,Prices!$A$5:$A$78,0))),CEILING(C72/INDEX(Prices!$K$5:$K$78,MATCH(A72,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A72,Prices!$A$5:$A$78,0)),G72))</f>
-        <v>2.770614</v>
+        <f aca="false">IF(C72&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A72,Prices!$A$5:$A$82,0))),CEILING(C72/INDEX(Prices!$K$5:$K$82,MATCH(A72,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A72,Prices!$A$5:$A$82,0)),G72))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12558,71 +12953,167 @@
         <v>373</v>
       </c>
       <c r="C73" s="4" t="n">
-        <f aca="false">SUMIF(Arm!$C$5:$C$32,A73,Arm!$D$5:$D$32)+SUMIF(Rover!$C$5:$C$39,A73,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A73,Hexapod!$D$5:$D$35)</f>
-        <v>45</v>
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A73,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A73,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A73,Hexapod!$D$5:$D$35)</f>
+        <v>0.2</v>
       </c>
       <c r="D73" s="35" t="n">
-        <f aca="false">INDEX(Prices!$E$5:$E$78,MATCH(A73,Prices!$A$5:$A$78,0))</f>
-        <v>100</v>
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A73,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
         <f aca="false">IF(C73&lt;=0,0,CEILING(C73/D73,1))</f>
         <v>1</v>
       </c>
       <c r="F73" s="8" t="n">
-        <f aca="false">INDEX(Prices!$H$5:$H$78,MATCH(A73,Prices!$A$5:$A$78,0))</f>
-        <v>5.99</v>
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A73,Prices!$A$5:$A$82,0))</f>
+        <v>19.93</v>
       </c>
       <c r="G73" s="31" t="n">
         <f aca="false">E73*F73</f>
+        <v>19.93</v>
+      </c>
+      <c r="H73" s="31" t="n">
+        <f aca="false">IF(C73&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A73,Prices!$A$5:$A$82,0))),CEILING(C73/INDEX(Prices!$K$5:$K$82,MATCH(A73,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A73,Prices!$A$5:$A$82,0)),G73))</f>
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A74,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A74,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A74,Hexapod!$D$5:$D$35)</f>
+        <v>4</v>
+      </c>
+      <c r="D74" s="35" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A74,Prices!$A$5:$A$82,0))</f>
+        <v>25</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <f aca="false">IF(C74&lt;=0,0,CEILING(C74/D74,1))</f>
+        <v>1</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A74,Prices!$A$5:$A$82,0))</f>
+        <v>4</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <f aca="false">E74*F74</f>
+        <v>4</v>
+      </c>
+      <c r="H74" s="31" t="n">
+        <f aca="false">IF(C74&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A74,Prices!$A$5:$A$82,0))),CEILING(C74/INDEX(Prices!$K$5:$K$82,MATCH(A74,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A74,Prices!$A$5:$A$82,0)),G74))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A75,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A75,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A75,Hexapod!$D$5:$D$35)</f>
+        <v>1</v>
+      </c>
+      <c r="D75" s="35" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A75,Prices!$A$5:$A$82,0))</f>
+        <v>1</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <f aca="false">IF(C75&lt;=0,0,CEILING(C75/D75,1))</f>
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A75,Prices!$A$5:$A$82,0))</f>
+        <v>2.770614</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <f aca="false">E75*F75</f>
+        <v>2.770614</v>
+      </c>
+      <c r="H75" s="31" t="n">
+        <f aca="false">IF(C75&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A75,Prices!$A$5:$A$82,0))),CEILING(C75/INDEX(Prices!$K$5:$K$82,MATCH(A75,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A75,Prices!$A$5:$A$82,0)),G75))</f>
+        <v>2.770614</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <f aca="false">SUMIF(Arm!$C$5:$C$36,A76,Arm!$D$5:$D$36)+SUMIF(Rover!$C$5:$C$39,A76,Rover!$D$5:$D$39)+SUMIF(Hexapod!$C$5:$C$35,A76,Hexapod!$D$5:$D$35)</f>
+        <v>45</v>
+      </c>
+      <c r="D76" s="35" t="n">
+        <f aca="false">INDEX(Prices!$E$5:$E$82,MATCH(A76,Prices!$A$5:$A$82,0))</f>
+        <v>100</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <f aca="false">IF(C76&lt;=0,0,CEILING(C76/D76,1))</f>
+        <v>1</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <f aca="false">INDEX(Prices!$H$5:$H$82,MATCH(A76,Prices!$A$5:$A$82,0))</f>
         <v>5.99</v>
       </c>
-      <c r="H73" s="31" t="n">
-        <f aca="false">IF(C73&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$78,MATCH(A73,Prices!$A$5:$A$78,0))),CEILING(C73/INDEX(Prices!$K$5:$K$78,MATCH(A73,Prices!$A$5:$A$78,0)),1)*INDEX(Prices!$L$5:$L$78,MATCH(A73,Prices!$A$5:$A$78,0)),G73))</f>
+      <c r="G76" s="31" t="n">
+        <f aca="false">E76*F76</f>
         <v>5.99</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="C75" s="35" t="n">
-        <f aca="false">Arm!D35+Rover!D42+Hexapod!D38</f>
+      <c r="H76" s="31" t="n">
+        <f aca="false">IF(C76&lt;=0,0,IF(ISNUMBER(INDEX(Prices!$L$5:$L$82,MATCH(A76,Prices!$A$5:$A$82,0))),CEILING(C76/INDEX(Prices!$K$5:$K$82,MATCH(A76,Prices!$A$5:$A$82,0)),1)*INDEX(Prices!$L$5:$L$82,MATCH(A76,Prices!$A$5:$A$82,0)),G76))</f>
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C78" s="35" t="n">
+        <f aca="false">Arm!D39+Rover!D42+Hexapod!D38</f>
         <v>1.033</v>
       </c>
-      <c r="G75" s="31" t="n">
-        <f aca="false">CEILING(C75,1)*Summary!$C$9</f>
+      <c r="G78" s="31" t="n">
+        <f aca="false">CEILING(C78,1)*Summary!$C$9</f>
         <v>29.98</v>
       </c>
-      <c r="H75" s="31" t="n">
-        <f aca="false">C75*Summary!$C$9</f>
+      <c r="H78" s="31" t="n">
+        <f aca="false">C78*Summary!$C$9</f>
         <v>15.48467</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G76" s="8" t="n">
-        <f aca="false">Arm!J36+Rover!J43+Hexapod!J39</f>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <f aca="false">Arm!J40+Rover!J43+Hexapod!J39</f>
         <v>1.3486176</v>
       </c>
-      <c r="H76" s="31" t="n">
-        <f aca="false">G76</f>
+      <c r="H79" s="31" t="n">
+        <f aca="false">G79</f>
         <v>1.3486176</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="33" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="G78" s="34" t="n">
-        <f aca="false">SUM(G5:G73)+G75+G76</f>
-        <v>788.9227576</v>
-      </c>
-      <c r="H78" s="34" t="n">
-        <f aca="false">SUM(H5:H73)+H75+H76</f>
-        <v>687.8542626</v>
+      <c r="G81" s="34" t="n">
+        <f aca="false">SUM(G5:G76)+G78+G79</f>
+        <v>797.7427576</v>
+      </c>
+      <c r="H81" s="34" t="n">
+        <f aca="false">SUM(H5:H76)+H78+H79</f>
+        <v>696.6742626</v>
       </c>
     </row>
   </sheetData>

--- a/docs/costs/robot_build_costs.xlsx
+++ b/docs/costs/robot_build_costs.xlsx
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="D42" s="29" t="n">
-        <v>0.303</v>
+        <v>0.335</v>
       </c>
       <c r="E42" s="8">
         <f>Summary!$C$9</f>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Round-2 slices; round 3 not sliced yet. 'Cost to buy' counts whole 1 kg spools.</t>
+          <t>Slices of 26 Oct 2026: 8 plates (chassis round 6, lid, sprockets, idlers, wheels 2 x 2, links 35 x 2). 'Cost to buy' counts whole 1 kg spools.</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="D43" s="29" t="n">
-        <v>30.4</v>
+        <v>33</v>
       </c>
       <c r="E43" s="31">
         <f>Summary!$C$11*Summary!$C$10</f>
